--- a/CB-Achmea/2025/Uitsluitingen.xlsx
+++ b/CB-Achmea/2025/Uitsluitingen.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7c741cee80ec8cf3/Financieel/IndexFondsenOnderzoek/KeuzeWelkIndexFonds/OnderzoekPerFonds/CB-Achmea/2025/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="58" documentId="11_AD4D7A0C205A6B9A452FA8E75FDB70E25BDEDD8D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{15F36926-B135-4DE8-A9C5-8A4621B6FE53}"/>
+  <xr:revisionPtr revIDLastSave="66" documentId="11_AD4D7A0C205A6B9A452FA8E75FDB70E25BDEDD8D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7AB794AB-ACB9-45B3-88E7-8CE0FE665958}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3657" uniqueCount="2888">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3656" uniqueCount="2887">
   <si>
     <t>US0378331005</t>
   </si>
@@ -7214,12 +7214,6 @@
     <t>BXP INC</t>
   </si>
   <si>
-    <t>MUENCHENER</t>
-  </si>
-  <si>
-    <t>RUECKVERSICHERUNGS-0,06</t>
-  </si>
-  <si>
     <t>TELE2 AB</t>
   </si>
   <si>
@@ -8703,6 +8697,9 @@
   </si>
   <si>
     <t>ETD USD BALANCE WITH 06738C</t>
+  </si>
+  <si>
+    <t>MUENCHENER RUECKVERSICHERUNGS</t>
   </si>
 </sst>
 </file>
@@ -12682,10 +12679,10 @@
         <v>1111</v>
       </c>
       <c r="B331" t="s">
-        <v>2391</v>
-      </c>
-      <c r="C331" s="2" t="s">
-        <v>2392</v>
+        <v>2886</v>
+      </c>
+      <c r="C331" s="2">
+        <v>0.06</v>
       </c>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.25">
@@ -12748,7 +12745,7 @@
         <v>2134</v>
       </c>
       <c r="B337" t="s">
-        <v>2393</v>
+        <v>2391</v>
       </c>
       <c r="C337" s="2">
         <v>0.06</v>
@@ -12759,7 +12756,7 @@
         <v>1987</v>
       </c>
       <c r="B338" t="s">
-        <v>2394</v>
+        <v>2392</v>
       </c>
       <c r="C338" s="2">
         <v>0.06</v>
@@ -12770,7 +12767,7 @@
         <v>173</v>
       </c>
       <c r="B339" t="s">
-        <v>2395</v>
+        <v>2393</v>
       </c>
       <c r="C339" s="2">
         <v>0.06</v>
@@ -12825,7 +12822,7 @@
         <v>2107</v>
       </c>
       <c r="B344" t="s">
-        <v>2396</v>
+        <v>2394</v>
       </c>
       <c r="C344" s="2">
         <v>0.06</v>
@@ -12833,10 +12830,10 @@
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>2397</v>
+        <v>2395</v>
       </c>
       <c r="B345" t="s">
-        <v>2398</v>
+        <v>2396</v>
       </c>
       <c r="C345" s="2">
         <v>0.06</v>
@@ -12855,7 +12852,7 @@
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>2399</v>
+        <v>2397</v>
       </c>
       <c r="B347" t="s">
         <v>158</v>
@@ -12924,7 +12921,7 @@
         <v>839</v>
       </c>
       <c r="B353" t="s">
-        <v>2400</v>
+        <v>2398</v>
       </c>
       <c r="C353" s="2">
         <v>0.05</v>
@@ -12943,10 +12940,10 @@
     </row>
     <row r="355" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>2401</v>
+        <v>2399</v>
       </c>
       <c r="B355" t="s">
-        <v>2402</v>
+        <v>2400</v>
       </c>
       <c r="C355" s="2">
         <v>0.05</v>
@@ -12957,7 +12954,7 @@
         <v>2222</v>
       </c>
       <c r="B356" t="s">
-        <v>2403</v>
+        <v>2401</v>
       </c>
       <c r="C356" s="2">
         <v>0.05</v>
@@ -12987,10 +12984,10 @@
     </row>
     <row r="359" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>2404</v>
+        <v>2402</v>
       </c>
       <c r="B359" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="C359" s="2">
         <v>0.05</v>
@@ -13053,10 +13050,10 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>2406</v>
+        <v>2404</v>
       </c>
       <c r="B365" t="s">
-        <v>2407</v>
+        <v>2405</v>
       </c>
       <c r="C365" s="2">
         <v>0.05</v>
@@ -13064,10 +13061,10 @@
     </row>
     <row r="366" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>2408</v>
+        <v>2406</v>
       </c>
       <c r="B366" t="s">
-        <v>2409</v>
+        <v>2407</v>
       </c>
       <c r="C366" s="2">
         <v>0.05</v>
@@ -13199,7 +13196,7 @@
         <v>1851</v>
       </c>
       <c r="B378" t="s">
-        <v>2410</v>
+        <v>2408</v>
       </c>
       <c r="C378" s="2">
         <v>0.04</v>
@@ -13210,7 +13207,7 @@
         <v>1250</v>
       </c>
       <c r="B379" t="s">
-        <v>2411</v>
+        <v>2409</v>
       </c>
       <c r="C379" s="2">
         <v>0.04</v>
@@ -13243,7 +13240,7 @@
         <v>2197</v>
       </c>
       <c r="B382" t="s">
-        <v>2412</v>
+        <v>2410</v>
       </c>
       <c r="C382" s="2">
         <v>0.04</v>
@@ -13298,7 +13295,7 @@
         <v>668</v>
       </c>
       <c r="B387" t="s">
-        <v>2413</v>
+        <v>2411</v>
       </c>
       <c r="C387" s="2">
         <v>0.04</v>
@@ -13328,10 +13325,10 @@
     </row>
     <row r="390" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
-        <v>2414</v>
+        <v>2412</v>
       </c>
       <c r="B390" t="s">
-        <v>2415</v>
+        <v>2413</v>
       </c>
       <c r="C390" s="2">
         <v>0.04</v>
@@ -13361,10 +13358,10 @@
     </row>
     <row r="393" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
-        <v>2416</v>
+        <v>2414</v>
       </c>
       <c r="B393" t="s">
-        <v>2417</v>
+        <v>2415</v>
       </c>
       <c r="C393" s="2">
         <v>0.04</v>
@@ -13386,7 +13383,7 @@
         <v>105</v>
       </c>
       <c r="B395" t="s">
-        <v>2418</v>
+        <v>2416</v>
       </c>
       <c r="C395" s="2">
         <v>0.04</v>
@@ -13416,10 +13413,10 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
-        <v>2419</v>
+        <v>2417</v>
       </c>
       <c r="B398" t="s">
-        <v>2420</v>
+        <v>2418</v>
       </c>
       <c r="C398" s="2">
         <v>0.04</v>
@@ -13430,7 +13427,7 @@
         <v>1878</v>
       </c>
       <c r="B399" t="s">
-        <v>2421</v>
+        <v>2419</v>
       </c>
       <c r="C399" s="2">
         <v>0.04</v>
@@ -13485,7 +13482,7 @@
         <v>332</v>
       </c>
       <c r="B404" t="s">
-        <v>2422</v>
+        <v>2420</v>
       </c>
       <c r="C404" s="2">
         <v>0.04</v>
@@ -13518,7 +13515,7 @@
         <v>558</v>
       </c>
       <c r="B407" t="s">
-        <v>2423</v>
+        <v>2421</v>
       </c>
       <c r="C407" s="2">
         <v>0.04</v>
@@ -13526,10 +13523,10 @@
     </row>
     <row r="408" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
-        <v>2424</v>
+        <v>2422</v>
       </c>
       <c r="B408" t="s">
-        <v>2425</v>
+        <v>2423</v>
       </c>
       <c r="C408" s="2">
         <v>0.04</v>
@@ -13584,7 +13581,7 @@
         <v>676</v>
       </c>
       <c r="B413" t="s">
-        <v>2426</v>
+        <v>2424</v>
       </c>
       <c r="C413" s="2">
         <v>0.03</v>
@@ -13592,10 +13589,10 @@
     </row>
     <row r="414" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
-        <v>2427</v>
+        <v>2425</v>
       </c>
       <c r="B414" t="s">
-        <v>2428</v>
+        <v>2426</v>
       </c>
       <c r="C414" s="2">
         <v>0.03</v>
@@ -13661,7 +13658,7 @@
         <v>1981</v>
       </c>
       <c r="B420" t="s">
-        <v>2429</v>
+        <v>2427</v>
       </c>
       <c r="C420" s="2">
         <v>0.03</v>
@@ -13694,7 +13691,7 @@
         <v>2187</v>
       </c>
       <c r="B423" t="s">
-        <v>2430</v>
+        <v>2428</v>
       </c>
       <c r="C423" s="2">
         <v>0.03</v>
@@ -13746,10 +13743,10 @@
     </row>
     <row r="428" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
-        <v>2431</v>
+        <v>2429</v>
       </c>
       <c r="B428" t="s">
-        <v>2432</v>
+        <v>2430</v>
       </c>
       <c r="C428" s="2">
         <v>0.02</v>
@@ -13757,10 +13754,10 @@
     </row>
     <row r="429" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
-        <v>2433</v>
+        <v>2431</v>
       </c>
       <c r="B429" t="s">
-        <v>2434</v>
+        <v>2432</v>
       </c>
       <c r="C429" s="2">
         <v>0.02</v>
@@ -13768,10 +13765,10 @@
     </row>
     <row r="430" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
-        <v>2435</v>
+        <v>2433</v>
       </c>
       <c r="B430" t="s">
-        <v>2436</v>
+        <v>2434</v>
       </c>
       <c r="C430" s="2">
         <v>0.02</v>
@@ -13812,10 +13809,10 @@
     </row>
     <row r="434" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
-        <v>2437</v>
+        <v>2435</v>
       </c>
       <c r="B434" t="s">
-        <v>2438</v>
+        <v>2436</v>
       </c>
       <c r="C434" s="2">
         <v>0.02</v>
@@ -13870,7 +13867,7 @@
         <v>1297</v>
       </c>
       <c r="B439" t="s">
-        <v>2439</v>
+        <v>2437</v>
       </c>
       <c r="C439" s="2">
         <v>0.02</v>
@@ -13892,7 +13889,7 @@
         <v>1569</v>
       </c>
       <c r="B441" t="s">
-        <v>2440</v>
+        <v>2438</v>
       </c>
       <c r="C441" s="2">
         <v>0.02</v>
@@ -13966,10 +13963,10 @@
     </row>
     <row r="448" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
-        <v>2441</v>
+        <v>2439</v>
       </c>
       <c r="B448" t="s">
-        <v>2442</v>
+        <v>2440</v>
       </c>
       <c r="C448" s="2">
         <v>0.02</v>
@@ -13991,7 +13988,7 @@
         <v>2109</v>
       </c>
       <c r="B450" t="s">
-        <v>2443</v>
+        <v>2441</v>
       </c>
       <c r="C450" s="2">
         <v>0.02</v>
@@ -13999,10 +13996,10 @@
     </row>
     <row r="451" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
-        <v>2444</v>
+        <v>2442</v>
       </c>
       <c r="B451" t="s">
-        <v>2445</v>
+        <v>2443</v>
       </c>
       <c r="C451" s="2">
         <v>0.02</v>
@@ -14021,7 +14018,7 @@
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
-        <v>2446</v>
+        <v>2444</v>
       </c>
       <c r="B453" t="s">
         <v>663</v>
@@ -14068,7 +14065,7 @@
         <v>2025</v>
       </c>
       <c r="B457" t="s">
-        <v>2447</v>
+        <v>2445</v>
       </c>
       <c r="C457" s="2">
         <v>0.02</v>
@@ -14145,7 +14142,7 @@
         <v>1882</v>
       </c>
       <c r="B464" t="s">
-        <v>2448</v>
+        <v>2446</v>
       </c>
       <c r="C464" s="2">
         <v>0.02</v>
@@ -14153,10 +14150,10 @@
     </row>
     <row r="465" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
-        <v>2449</v>
+        <v>2447</v>
       </c>
       <c r="B465" t="s">
-        <v>2450</v>
+        <v>2448</v>
       </c>
       <c r="C465" s="2">
         <v>0.02</v>
@@ -14164,7 +14161,7 @@
     </row>
     <row r="466" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
-        <v>2451</v>
+        <v>2449</v>
       </c>
       <c r="B466" t="s">
         <v>519</v>
@@ -14277,7 +14274,7 @@
         <v>2174</v>
       </c>
       <c r="B476" t="s">
-        <v>2452</v>
+        <v>2450</v>
       </c>
       <c r="C476" s="2">
         <v>0.01</v>
@@ -14285,7 +14282,7 @@
     </row>
     <row r="477" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
-        <v>2453</v>
+        <v>2451</v>
       </c>
       <c r="B477" t="s">
         <v>725</v>
@@ -14299,7 +14296,7 @@
         <v>1974</v>
       </c>
       <c r="B478" t="s">
-        <v>2454</v>
+        <v>2452</v>
       </c>
       <c r="C478" s="2">
         <v>0.01</v>
@@ -14310,7 +14307,7 @@
         <v>323</v>
       </c>
       <c r="B479" t="s">
-        <v>2455</v>
+        <v>2453</v>
       </c>
       <c r="C479" s="2">
         <v>0.01</v>
@@ -14400,7 +14397,6 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79DB0B66-0A1C-4A43-88B1-CBC963950DC5}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:D1634"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -14423,7 +14419,7 @@
         <v>1321</v>
       </c>
     </row>
-    <row r="2" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -14438,7 +14434,7 @@
         <v>US67066G1040</v>
       </c>
     </row>
-    <row r="3" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -14453,7 +14449,7 @@
         <v>US0378331005</v>
       </c>
     </row>
-    <row r="4" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -14468,7 +14464,7 @@
         <v>US5949181045</v>
       </c>
     </row>
-    <row r="5" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>1322</v>
       </c>
@@ -14483,7 +14479,7 @@
         <v>US0231351067</v>
       </c>
     </row>
-    <row r="6" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>1323</v>
       </c>
@@ -14498,7 +14494,7 @@
         <v>US02079K3059</v>
       </c>
     </row>
-    <row r="7" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>120</v>
       </c>
@@ -14513,7 +14509,7 @@
         <v>US11135F1012</v>
       </c>
     </row>
-    <row r="8" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>1324</v>
       </c>
@@ -14528,9 +14524,9 @@
         <v>US02079K1079</v>
       </c>
     </row>
-    <row r="9" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>2456</v>
+        <v>2454</v>
       </c>
       <c r="B9">
         <v>1.72</v>
@@ -14558,7 +14554,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="11" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -14573,7 +14569,7 @@
         <v>US46625H1005</v>
       </c>
     </row>
-    <row r="12" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>1341</v>
       </c>
@@ -14603,7 +14599,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="14" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>1325</v>
       </c>
@@ -14633,7 +14629,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="16" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>22</v>
       </c>
@@ -14648,7 +14644,7 @@
         <v>US4781601046</v>
       </c>
     </row>
-    <row r="17" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>64</v>
       </c>
@@ -14663,7 +14659,7 @@
         <v>US9311421039</v>
       </c>
     </row>
-    <row r="18" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>1330</v>
       </c>
@@ -14678,7 +14674,7 @@
         <v>US57636Q1040</v>
       </c>
     </row>
-    <row r="19" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>45</v>
       </c>
@@ -14693,7 +14689,7 @@
         <v>NL0010273215</v>
       </c>
     </row>
-    <row r="20" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>48</v>
       </c>
@@ -14708,9 +14704,9 @@
         <v>US00287Y1091</v>
       </c>
     </row>
-    <row r="21" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>2457</v>
+        <v>2455</v>
       </c>
       <c r="B21">
         <v>0.48</v>
@@ -14723,7 +14719,7 @@
         <v>US69608A1088</v>
       </c>
     </row>
-    <row r="22" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>59</v>
       </c>
@@ -14738,7 +14734,7 @@
         <v>US64110L1061</v>
       </c>
     </row>
-    <row r="23" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>37</v>
       </c>
@@ -14753,7 +14749,7 @@
         <v>US0605051046</v>
       </c>
     </row>
-    <row r="24" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>54</v>
       </c>
@@ -14768,7 +14764,7 @@
         <v>US22160K1051</v>
       </c>
     </row>
-    <row r="25" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>223</v>
       </c>
@@ -14783,7 +14779,7 @@
         <v>US0079031078</v>
       </c>
     </row>
-    <row r="26" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>1329</v>
       </c>
@@ -14798,7 +14794,7 @@
         <v>US4370761029</v>
       </c>
     </row>
-    <row r="27" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>1327</v>
       </c>
@@ -14813,7 +14809,7 @@
         <v>US7427181091</v>
       </c>
     </row>
-    <row r="28" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>109</v>
       </c>
@@ -14828,7 +14824,7 @@
         <v>US68389X1054</v>
       </c>
     </row>
-    <row r="29" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>2300</v>
       </c>
@@ -14843,7 +14839,7 @@
         <v>US3696043013</v>
       </c>
     </row>
-    <row r="30" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>182</v>
       </c>
@@ -14858,7 +14854,7 @@
         <v>US5951121038</v>
       </c>
     </row>
-    <row r="31" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>1334</v>
       </c>
@@ -14873,7 +14869,7 @@
         <v>US17275R1023</v>
       </c>
     </row>
-    <row r="32" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>1344</v>
       </c>
@@ -14888,7 +14884,7 @@
         <v>US9497461015</v>
       </c>
     </row>
-    <row r="33" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>16</v>
       </c>
@@ -14918,7 +14914,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="35" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>1333</v>
       </c>
@@ -14933,7 +14929,7 @@
         <v>CH0012032048</v>
       </c>
     </row>
-    <row r="36" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>115</v>
       </c>
@@ -14948,7 +14944,7 @@
         <v>GB0009895292</v>
       </c>
     </row>
-    <row r="37" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>1335</v>
       </c>
@@ -14963,7 +14959,7 @@
         <v>US1912161007</v>
       </c>
     </row>
-    <row r="38" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>1358</v>
       </c>
@@ -14978,7 +14974,7 @@
         <v>US4592001014</v>
       </c>
     </row>
-    <row r="39" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>288</v>
       </c>
@@ -14993,7 +14989,7 @@
         <v>GB0005405286</v>
       </c>
     </row>
-    <row r="40" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>214</v>
       </c>
@@ -15008,7 +15004,7 @@
         <v>US1491231015</v>
       </c>
     </row>
-    <row r="41" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>1366</v>
       </c>
@@ -15023,7 +15019,7 @@
         <v>US38141G1040</v>
       </c>
     </row>
-    <row r="42" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>78</v>
       </c>
@@ -15038,7 +15034,7 @@
         <v>US58933Y1055</v>
       </c>
     </row>
-    <row r="43" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>129</v>
       </c>
@@ -15053,7 +15049,7 @@
         <v>CH0012005267</v>
       </c>
     </row>
-    <row r="44" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>28</v>
       </c>
@@ -15068,7 +15064,7 @@
         <v>CH0038863350</v>
       </c>
     </row>
-    <row r="45" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>1352</v>
       </c>
@@ -15083,7 +15079,7 @@
         <v>DE0007164600</v>
       </c>
     </row>
-    <row r="46" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>2301</v>
       </c>
@@ -15115,7 +15111,7 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>2458</v>
+        <v>2456</v>
       </c>
       <c r="B48">
         <v>0.28999999999999998</v>
@@ -15128,7 +15124,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="49" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>292</v>
       </c>
@@ -15158,7 +15154,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="51" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>104</v>
       </c>
@@ -15173,7 +15169,7 @@
         <v>US1729674242</v>
       </c>
     </row>
-    <row r="52" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>76</v>
       </c>
@@ -15188,7 +15184,7 @@
         <v>US0028241000</v>
       </c>
     </row>
-    <row r="53" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>1339</v>
       </c>
@@ -15203,7 +15199,7 @@
         <v>US5801351017</v>
       </c>
     </row>
-    <row r="54" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>136</v>
       </c>
@@ -15218,7 +15214,7 @@
         <v>US5128073062</v>
       </c>
     </row>
-    <row r="55" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>113</v>
       </c>
@@ -15233,7 +15229,7 @@
         <v>US6174464486</v>
       </c>
     </row>
-    <row r="56" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>2294</v>
       </c>
@@ -15248,7 +15244,7 @@
         <v>GB00BP6MXD84</v>
       </c>
     </row>
-    <row r="57" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>1353</v>
       </c>
@@ -15263,7 +15259,7 @@
         <v>DE0007236101</v>
       </c>
     </row>
-    <row r="58" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>1368</v>
       </c>
@@ -15278,7 +15274,7 @@
         <v>US0258161092</v>
       </c>
     </row>
-    <row r="59" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>1328</v>
       </c>
@@ -15293,7 +15289,7 @@
         <v>US2546871060</v>
       </c>
     </row>
-    <row r="60" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>1354</v>
       </c>
@@ -15308,7 +15304,7 @@
         <v>US0382221051</v>
       </c>
     </row>
-    <row r="61" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>180</v>
       </c>
@@ -15323,7 +15319,7 @@
         <v>JP3633400001</v>
       </c>
     </row>
-    <row r="62" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>600</v>
       </c>
@@ -15338,7 +15334,7 @@
         <v>US46120E6023</v>
       </c>
     </row>
-    <row r="63" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>158</v>
       </c>
@@ -15346,14 +15342,14 @@
         <v>0.24</v>
       </c>
       <c r="C63" t="s">
-        <v>2399</v>
+        <v>2397</v>
       </c>
       <c r="D63" t="str">
         <f>VLOOKUP(C63,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
         <v>IE000S9YS762</v>
       </c>
     </row>
-    <row r="64" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>1355</v>
       </c>
@@ -15383,7 +15379,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="66" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>1336</v>
       </c>
@@ -15398,7 +15394,7 @@
         <v>FR0000121014</v>
       </c>
     </row>
-    <row r="67" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>69</v>
       </c>
@@ -15413,7 +15409,7 @@
         <v>US4612021034</v>
       </c>
     </row>
-    <row r="68" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>101</v>
       </c>
@@ -15428,7 +15424,7 @@
         <v>US7475251036</v>
       </c>
     </row>
-    <row r="69" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>1399</v>
       </c>
@@ -15458,7 +15454,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="71" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>208</v>
       </c>
@@ -15473,7 +15469,7 @@
         <v>AU000000CBA7</v>
       </c>
     </row>
-    <row r="72" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>178</v>
       </c>
@@ -15488,22 +15484,22 @@
         <v>US00206R1023</v>
       </c>
     </row>
-    <row r="73" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>2425</v>
+        <v>2423</v>
       </c>
       <c r="B73">
         <v>0.21</v>
       </c>
       <c r="C73" t="s">
-        <v>2424</v>
+        <v>2422</v>
       </c>
       <c r="D73" t="str">
         <f>VLOOKUP(C73,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
         <v>US36828A1016</v>
       </c>
     </row>
-    <row r="74" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>1364</v>
       </c>
@@ -15518,7 +15514,7 @@
         <v>DE0008404005</v>
       </c>
     </row>
-    <row r="75" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>647</v>
       </c>
@@ -15548,7 +15544,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="77" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>1369</v>
       </c>
@@ -15563,7 +15559,7 @@
         <v>US8085131055</v>
       </c>
     </row>
-    <row r="78" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>167</v>
       </c>
@@ -15578,7 +15574,7 @@
         <v>US92343V1044</v>
       </c>
     </row>
-    <row r="79" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>1382</v>
       </c>
@@ -15593,7 +15589,7 @@
         <v>US8725401090</v>
       </c>
     </row>
-    <row r="80" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>1331</v>
       </c>
@@ -15623,7 +15619,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="82" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>227</v>
       </c>
@@ -15638,7 +15634,7 @@
         <v>US78409V1044</v>
       </c>
     </row>
-    <row r="83" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>1360</v>
       </c>
@@ -15653,7 +15649,7 @@
         <v>CA8911605092</v>
       </c>
     </row>
-    <row r="84" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>1337</v>
       </c>
@@ -15668,7 +15664,7 @@
         <v>IE00B4BNMY34</v>
       </c>
     </row>
-    <row r="85" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>1479</v>
       </c>
@@ -15683,7 +15679,7 @@
         <v>US0320951017</v>
       </c>
     </row>
-    <row r="86" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>1357</v>
       </c>
@@ -15698,7 +15694,7 @@
         <v>DK0062498333</v>
       </c>
     </row>
-    <row r="87" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>652</v>
       </c>
@@ -15713,7 +15709,7 @@
         <v>US90353T1007</v>
       </c>
     </row>
-    <row r="88" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>243</v>
       </c>
@@ -15728,7 +15724,7 @@
         <v>US4824801009</v>
       </c>
     </row>
-    <row r="89" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>135</v>
       </c>
@@ -15773,7 +15769,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="92" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>122</v>
       </c>
@@ -15788,7 +15784,7 @@
         <v>JP3435000009</v>
       </c>
     </row>
-    <row r="93" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>188</v>
       </c>
@@ -15803,9 +15799,9 @@
         <v>US09290D1019</v>
       </c>
     </row>
-    <row r="94" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>2459</v>
+        <v>2457</v>
       </c>
       <c r="B94">
         <v>0.19</v>
@@ -15833,7 +15829,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="96" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>370</v>
       </c>
@@ -15878,7 +15874,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="99" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>35</v>
       </c>
@@ -15908,7 +15904,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="101" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>272</v>
       </c>
@@ -15946,14 +15942,14 @@
         <v>0.17</v>
       </c>
       <c r="C103" t="s">
-        <v>2460</v>
+        <v>2458</v>
       </c>
       <c r="D103" t="e">
         <f>VLOOKUP(C103,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="104" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>74</v>
       </c>
@@ -15968,7 +15964,7 @@
         <v>US7170811035</v>
       </c>
     </row>
-    <row r="105" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>1427</v>
       </c>
@@ -15983,7 +15979,7 @@
         <v>US1011371077</v>
       </c>
     </row>
-    <row r="106" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>924</v>
       </c>
@@ -15998,9 +15994,9 @@
         <v>US0404132054</v>
       </c>
     </row>
-    <row r="107" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>2461</v>
+        <v>2459</v>
       </c>
       <c r="B107">
         <v>0.17</v>
@@ -16028,7 +16024,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="109" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>94</v>
       </c>
@@ -16073,7 +16069,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="112" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>1347</v>
       </c>
@@ -16088,7 +16084,7 @@
         <v>US5486611073</v>
       </c>
     </row>
-    <row r="113" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>1501</v>
       </c>
@@ -16120,7 +16116,7 @@
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>2462</v>
+        <v>2460</v>
       </c>
       <c r="B115">
         <v>0.16</v>
@@ -16163,7 +16159,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="118" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>1134</v>
       </c>
@@ -16193,7 +16189,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="120" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>355</v>
       </c>
@@ -16210,7 +16206,7 @@
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>2463</v>
+        <v>2461</v>
       </c>
       <c r="B121">
         <v>0.15</v>
@@ -16238,7 +16234,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="123" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>283</v>
       </c>
@@ -16253,7 +16249,7 @@
         <v>US8636671013</v>
       </c>
     </row>
-    <row r="124" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>90</v>
       </c>
@@ -16283,7 +16279,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="126" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>1611</v>
       </c>
@@ -16298,7 +16294,7 @@
         <v>IT0005239360</v>
       </c>
     </row>
-    <row r="127" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>1442</v>
       </c>
@@ -16313,7 +16309,7 @@
         <v>JP3890350006</v>
       </c>
     </row>
-    <row r="128" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>1361</v>
       </c>
@@ -16328,7 +16324,7 @@
         <v>US2441991054</v>
       </c>
     </row>
-    <row r="129" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>1396</v>
       </c>
@@ -16358,7 +16354,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="131" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>1434</v>
       </c>
@@ -16403,7 +16399,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="134" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>1076</v>
       </c>
@@ -16433,7 +16429,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="136" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>1440</v>
       </c>
@@ -16448,7 +16444,7 @@
         <v>US6516391066</v>
       </c>
     </row>
-    <row r="137" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>1332</v>
       </c>
@@ -16463,7 +16459,7 @@
         <v>US20030N1019</v>
       </c>
     </row>
-    <row r="138" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>131</v>
       </c>
@@ -16480,7 +16476,7 @@
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>2464</v>
+        <v>2462</v>
       </c>
       <c r="B139">
         <v>0.14000000000000001</v>
@@ -16495,20 +16491,20 @@
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>2465</v>
+        <v>2463</v>
       </c>
       <c r="B140">
         <v>0.13</v>
       </c>
       <c r="C140" t="s">
-        <v>2466</v>
+        <v>2464</v>
       </c>
       <c r="D140" t="e">
         <f>VLOOKUP(C140,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="141" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>1786</v>
       </c>
@@ -16523,7 +16519,7 @@
         <v>DE000ENER6Y0</v>
       </c>
     </row>
-    <row r="142" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>1346</v>
       </c>
@@ -16538,7 +16534,7 @@
         <v>US1101221083</v>
       </c>
     </row>
-    <row r="143" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>1345</v>
       </c>
@@ -16553,7 +16549,7 @@
         <v>HK0000069689</v>
       </c>
     </row>
-    <row r="144" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>1362</v>
       </c>
@@ -16583,7 +16579,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="146" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>1180</v>
       </c>
@@ -16613,7 +16609,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="148" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>441</v>
       </c>
@@ -16628,7 +16624,7 @@
         <v>US58155Q1031</v>
       </c>
     </row>
-    <row r="149" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>170</v>
       </c>
@@ -16643,7 +16639,7 @@
         <v>US0530151036</v>
       </c>
     </row>
-    <row r="150" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>1394</v>
       </c>
@@ -16690,13 +16686,13 @@
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>2467</v>
+        <v>2465</v>
       </c>
       <c r="B153">
         <v>0.12</v>
       </c>
       <c r="C153" t="s">
-        <v>2468</v>
+        <v>2466</v>
       </c>
       <c r="D153" t="e">
         <f>VLOOKUP(C153,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -16718,7 +16714,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="155" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>1240</v>
       </c>
@@ -16733,7 +16729,7 @@
         <v>JP3122400009</v>
       </c>
     </row>
-    <row r="156" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>165</v>
       </c>
@@ -16750,20 +16746,20 @@
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>2469</v>
+        <v>2467</v>
       </c>
       <c r="B157">
         <v>0.12</v>
       </c>
       <c r="C157" t="s">
-        <v>2470</v>
+        <v>2468</v>
       </c>
       <c r="D157" t="e">
         <f>VLOOKUP(C157,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="158" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>1444</v>
       </c>
@@ -16778,7 +16774,7 @@
         <v>IT0000072618</v>
       </c>
     </row>
-    <row r="159" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>1389</v>
       </c>
@@ -16793,7 +16789,7 @@
         <v>US12572Q1058</v>
       </c>
     </row>
-    <row r="160" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>253</v>
       </c>
@@ -16823,7 +16819,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="162" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>704</v>
       </c>
@@ -16838,7 +16834,7 @@
         <v>FR0000121667</v>
       </c>
     </row>
-    <row r="163" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>247</v>
       </c>
@@ -16855,13 +16851,13 @@
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>2471</v>
+        <v>2469</v>
       </c>
       <c r="B164">
         <v>0.11</v>
       </c>
       <c r="C164" t="s">
-        <v>2472</v>
+        <v>2470</v>
       </c>
       <c r="D164" t="e">
         <f>VLOOKUP(C164,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -16883,7 +16879,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="166" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>623</v>
       </c>
@@ -16913,7 +16909,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="168" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>724</v>
       </c>
@@ -16943,7 +16939,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="170" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>297</v>
       </c>
@@ -16975,13 +16971,13 @@
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>2473</v>
+        <v>2471</v>
       </c>
       <c r="B172">
         <v>0.11</v>
       </c>
       <c r="C172" t="s">
-        <v>2474</v>
+        <v>2472</v>
       </c>
       <c r="D172" t="e">
         <f>VLOOKUP(C172,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -17003,7 +16999,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="174" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>80</v>
       </c>
@@ -17078,7 +17074,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="179" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>1453</v>
       </c>
@@ -17093,7 +17089,7 @@
         <v>DE0008430026</v>
       </c>
     </row>
-    <row r="180" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>1363</v>
       </c>
@@ -17108,9 +17104,9 @@
         <v>US88579Y1010</v>
       </c>
     </row>
-    <row r="181" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>2475</v>
+        <v>2473</v>
       </c>
       <c r="B181">
         <v>0.1</v>
@@ -17123,7 +17119,7 @@
         <v>US25809K1051</v>
       </c>
     </row>
-    <row r="182" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>1830</v>
       </c>
@@ -17168,7 +17164,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="185" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>1395</v>
       </c>
@@ -17183,7 +17179,7 @@
         <v>AU000000WBC1</v>
       </c>
     </row>
-    <row r="186" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>665</v>
       </c>
@@ -17198,7 +17194,7 @@
         <v>AU000000NAB4</v>
       </c>
     </row>
-    <row r="187" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>249</v>
       </c>
@@ -17215,20 +17211,20 @@
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>2476</v>
+        <v>2474</v>
       </c>
       <c r="B188">
         <v>0.1</v>
       </c>
       <c r="C188" t="s">
-        <v>2477</v>
+        <v>2475</v>
       </c>
       <c r="D188" t="e">
         <f>VLOOKUP(C188,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="189" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>205</v>
       </c>
@@ -17243,7 +17239,7 @@
         <v>IE00BK9ZQ967</v>
       </c>
     </row>
-    <row r="190" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>630</v>
       </c>
@@ -17258,7 +17254,7 @@
         <v>NL0011821202</v>
       </c>
     </row>
-    <row r="191" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>1379</v>
       </c>
@@ -17273,9 +17269,9 @@
         <v>IT0003128367</v>
       </c>
     </row>
-    <row r="192" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>2478</v>
+        <v>2476</v>
       </c>
       <c r="B192">
         <v>0.1</v>
@@ -17288,7 +17284,7 @@
         <v>IE0001827041</v>
       </c>
     </row>
-    <row r="193" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>1477</v>
       </c>
@@ -17320,7 +17316,7 @@
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>2479</v>
+        <v>2477</v>
       </c>
       <c r="B195">
         <v>0.1</v>
@@ -17333,7 +17329,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="196" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>1435</v>
       </c>
@@ -17363,7 +17359,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="198" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>1458</v>
       </c>
@@ -17378,9 +17374,9 @@
         <v>CA1360691010</v>
       </c>
     </row>
-    <row r="199" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>2480</v>
+        <v>2478</v>
       </c>
       <c r="B199">
         <v>0.1</v>
@@ -17393,7 +17389,7 @@
         <v>US7707001027</v>
       </c>
     </row>
-    <row r="200" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>409</v>
       </c>
@@ -17483,7 +17479,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="206" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>1476</v>
       </c>
@@ -17500,7 +17496,7 @@
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>2481</v>
+        <v>2479</v>
       </c>
       <c r="B207">
         <v>0.1</v>
@@ -17513,7 +17509,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="208" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>1867</v>
       </c>
@@ -17528,7 +17524,7 @@
         <v>JP3900000005</v>
       </c>
     </row>
-    <row r="209" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>333</v>
       </c>
@@ -17543,7 +17539,7 @@
         <v>FR0000052292</v>
       </c>
     </row>
-    <row r="210" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>1387</v>
       </c>
@@ -17558,7 +17554,7 @@
         <v>US37045V1008</v>
       </c>
     </row>
-    <row r="211" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>1398</v>
       </c>
@@ -17573,7 +17569,7 @@
         <v>JP3970300004</v>
       </c>
     </row>
-    <row r="212" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>503</v>
       </c>
@@ -17603,7 +17599,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="214" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>1150</v>
       </c>
@@ -17633,7 +17629,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="216" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>277</v>
       </c>
@@ -17663,7 +17659,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="218" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>1415</v>
       </c>
@@ -17693,9 +17689,9 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="220" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>2482</v>
+        <v>2480</v>
       </c>
       <c r="B220">
         <v>0.09</v>
@@ -17708,7 +17704,7 @@
         <v>US1255231003</v>
       </c>
     </row>
-    <row r="221" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>391</v>
       </c>
@@ -17738,7 +17734,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="223" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>368</v>
       </c>
@@ -17813,7 +17809,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="228" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>1466</v>
       </c>
@@ -17828,7 +17824,7 @@
         <v>US5719032022</v>
       </c>
     </row>
-    <row r="229" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>2325</v>
       </c>
@@ -17873,7 +17869,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="232" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>1662</v>
       </c>
@@ -17905,7 +17901,7 @@
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>2483</v>
+        <v>2481</v>
       </c>
       <c r="B234">
         <v>0.09</v>
@@ -17918,7 +17914,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="235" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>501</v>
       </c>
@@ -17933,15 +17929,15 @@
         <v>US2310211063</v>
       </c>
     </row>
-    <row r="236" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>2484</v>
+        <v>2482</v>
       </c>
       <c r="B236">
         <v>0.09</v>
       </c>
       <c r="C236" t="s">
-        <v>2416</v>
+        <v>2414</v>
       </c>
       <c r="D236" t="str">
         <f>VLOOKUP(C236,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -17993,7 +17989,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="240" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>736</v>
       </c>
@@ -18008,7 +18004,7 @@
         <v>DE0005140008</v>
       </c>
     </row>
-    <row r="241" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>1182</v>
       </c>
@@ -18053,7 +18049,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="244" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>1437</v>
       </c>
@@ -18068,7 +18064,7 @@
         <v>US35671D8570</v>
       </c>
     </row>
-    <row r="245" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>2323</v>
       </c>
@@ -18083,7 +18079,7 @@
         <v>IE000IVNQZ81</v>
       </c>
     </row>
-    <row r="246" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>1356</v>
       </c>
@@ -18113,7 +18109,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="248" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>1144</v>
       </c>
@@ -18130,7 +18126,7 @@
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>2485</v>
+        <v>2483</v>
       </c>
       <c r="B249">
         <v>0.08</v>
@@ -18173,7 +18169,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="252" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>1393</v>
       </c>
@@ -18190,20 +18186,20 @@
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>2486</v>
+        <v>2484</v>
       </c>
       <c r="B253">
         <v>0.08</v>
       </c>
       <c r="C253" t="s">
-        <v>2487</v>
+        <v>2485</v>
       </c>
       <c r="D253" t="e">
         <f>VLOOKUP(C253,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="254" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>305</v>
       </c>
@@ -18218,7 +18214,7 @@
         <v>US31428X1063</v>
       </c>
     </row>
-    <row r="255" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>1528</v>
       </c>
@@ -18248,7 +18244,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="257" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>1205</v>
       </c>
@@ -18310,7 +18306,7 @@
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>2488</v>
+        <v>2486</v>
       </c>
       <c r="B261">
         <v>0.08</v>
@@ -18338,7 +18334,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="263" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>256</v>
       </c>
@@ -18355,13 +18351,13 @@
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>2489</v>
+        <v>2487</v>
       </c>
       <c r="B264">
         <v>0.08</v>
       </c>
       <c r="C264" t="s">
-        <v>2490</v>
+        <v>2488</v>
       </c>
       <c r="D264" t="e">
         <f>VLOOKUP(C264,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -18385,7 +18381,7 @@
     </row>
     <row r="266" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>2491</v>
+        <v>2489</v>
       </c>
       <c r="B266">
         <v>0.08</v>
@@ -18398,7 +18394,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="267" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>195</v>
       </c>
@@ -18428,7 +18424,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="269" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>881</v>
       </c>
@@ -18443,9 +18439,9 @@
         <v>US0527691069</v>
       </c>
     </row>
-    <row r="270" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>2492</v>
+        <v>2490</v>
       </c>
       <c r="B270">
         <v>7.0000000000000007E-2</v>
@@ -18475,13 +18471,13 @@
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>2493</v>
+        <v>2491</v>
       </c>
       <c r="B272">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="C272" t="s">
-        <v>2494</v>
+        <v>2492</v>
       </c>
       <c r="D272" t="e">
         <f>VLOOKUP(C272,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -18503,7 +18499,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="274" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>1516</v>
       </c>
@@ -18518,7 +18514,7 @@
         <v>FI4000297767</v>
       </c>
     </row>
-    <row r="275" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>2306</v>
       </c>
@@ -18533,7 +18529,7 @@
         <v>US03073E1055</v>
       </c>
     </row>
-    <row r="276" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>142</v>
       </c>
@@ -18563,7 +18559,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="278" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>1507</v>
       </c>
@@ -18578,7 +18574,7 @@
         <v>US8288061091</v>
       </c>
     </row>
-    <row r="279" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>1973</v>
       </c>
@@ -18608,7 +18604,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="281" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>260</v>
       </c>
@@ -18623,7 +18619,7 @@
         <v>US0010551028</v>
       </c>
     </row>
-    <row r="282" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>1462</v>
       </c>
@@ -18638,9 +18634,9 @@
         <v>FR0000120644</v>
       </c>
     </row>
-    <row r="283" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>2495</v>
+        <v>2493</v>
       </c>
       <c r="B283">
         <v>7.0000000000000007E-2</v>
@@ -18653,7 +18649,7 @@
         <v>US92537N1081</v>
       </c>
     </row>
-    <row r="284" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>1096</v>
       </c>
@@ -18668,9 +18664,9 @@
         <v>US7782961038</v>
       </c>
     </row>
-    <row r="285" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>2496</v>
+        <v>2494</v>
       </c>
       <c r="B285">
         <v>7.0000000000000007E-2</v>
@@ -18683,7 +18679,7 @@
         <v>AN8068571086</v>
       </c>
     </row>
-    <row r="286" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>1170</v>
       </c>
@@ -18743,7 +18739,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="290" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>1411</v>
       </c>
@@ -18788,7 +18784,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="293" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>1130</v>
       </c>
@@ -18803,7 +18799,7 @@
         <v>US9581021055</v>
       </c>
     </row>
-    <row r="294" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>1388</v>
       </c>
@@ -18818,7 +18814,7 @@
         <v>US98978V1035</v>
       </c>
     </row>
-    <row r="295" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>1142</v>
       </c>
@@ -18850,7 +18846,7 @@
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>2497</v>
+        <v>2495</v>
       </c>
       <c r="B297">
         <v>7.0000000000000007E-2</v>
@@ -18893,7 +18889,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="300" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>133</v>
       </c>
@@ -18923,7 +18919,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="302" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>722</v>
       </c>
@@ -18953,7 +18949,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="304" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>916</v>
       </c>
@@ -18998,9 +18994,9 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="307" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>2498</v>
+        <v>2496</v>
       </c>
       <c r="B307">
         <v>0.06</v>
@@ -19028,7 +19024,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="309" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>1071</v>
       </c>
@@ -19088,7 +19084,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="313" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>31</v>
       </c>
@@ -19148,7 +19144,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="317" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>753</v>
       </c>
@@ -19193,7 +19189,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="320" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>636</v>
       </c>
@@ -19223,7 +19219,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="322" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>793</v>
       </c>
@@ -19238,7 +19234,7 @@
         <v>GB00BD6K4575</v>
       </c>
     </row>
-    <row r="323" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>1726</v>
       </c>
@@ -19268,7 +19264,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="325" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>268</v>
       </c>
@@ -19283,7 +19279,7 @@
         <v>US3453708600</v>
       </c>
     </row>
-    <row r="326" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>639</v>
       </c>
@@ -19315,7 +19311,7 @@
     </row>
     <row r="328" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>2499</v>
+        <v>2497</v>
       </c>
       <c r="B328">
         <v>0.06</v>
@@ -19328,7 +19324,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="329" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>1491</v>
       </c>
@@ -19343,7 +19339,7 @@
         <v>SE0000115446</v>
       </c>
     </row>
-    <row r="330" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>1515</v>
       </c>
@@ -19373,7 +19369,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="332" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>814</v>
       </c>
@@ -19388,7 +19384,7 @@
         <v>ES0140609019</v>
       </c>
     </row>
-    <row r="333" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>1503</v>
       </c>
@@ -19418,7 +19414,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="335" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>1478</v>
       </c>
@@ -19465,7 +19461,7 @@
     </row>
     <row r="338" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
-        <v>2500</v>
+        <v>2498</v>
       </c>
       <c r="B338">
         <v>0.06</v>
@@ -19478,7 +19474,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="339" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>1157</v>
       </c>
@@ -19501,7 +19497,7 @@
         <v>0.06</v>
       </c>
       <c r="C340" t="s">
-        <v>2501</v>
+        <v>2499</v>
       </c>
       <c r="D340" t="e">
         <f>VLOOKUP(C340,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -19523,7 +19519,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="342" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>1267</v>
       </c>
@@ -19538,7 +19534,7 @@
         <v>US14149Y1082</v>
       </c>
     </row>
-    <row r="343" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>612</v>
       </c>
@@ -19553,7 +19549,7 @@
         <v>US2855121099</v>
       </c>
     </row>
-    <row r="344" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>1580</v>
       </c>
@@ -19583,7 +19579,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="346" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>584</v>
       </c>
@@ -19645,7 +19641,7 @@
     </row>
     <row r="350" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>2502</v>
+        <v>2500</v>
       </c>
       <c r="B350">
         <v>0.06</v>
@@ -19658,7 +19654,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="351" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>1386</v>
       </c>
@@ -19673,7 +19669,7 @@
         <v>DE000BASF111</v>
       </c>
     </row>
-    <row r="352" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>654</v>
       </c>
@@ -19808,7 +19804,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="361" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>586</v>
       </c>
@@ -19825,13 +19821,13 @@
     </row>
     <row r="362" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>2503</v>
+        <v>2501</v>
       </c>
       <c r="B362">
         <v>0.06</v>
       </c>
       <c r="C362" t="s">
-        <v>2504</v>
+        <v>2502</v>
       </c>
       <c r="D362" t="e">
         <f>VLOOKUP(C362,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -19840,20 +19836,20 @@
     </row>
     <row r="363" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>2505</v>
+        <v>2503</v>
       </c>
       <c r="B363">
         <v>0.06</v>
       </c>
       <c r="C363" t="s">
-        <v>2506</v>
+        <v>2504</v>
       </c>
       <c r="D363" t="e">
         <f>VLOOKUP(C363,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="364" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
         <v>1551</v>
       </c>
@@ -19885,20 +19881,20 @@
     </row>
     <row r="366" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>2507</v>
+        <v>2505</v>
       </c>
       <c r="B366">
         <v>0.05</v>
       </c>
       <c r="C366" t="s">
-        <v>2508</v>
+        <v>2506</v>
       </c>
       <c r="D366" t="e">
         <f>VLOOKUP(C366,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="367" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
         <v>561</v>
       </c>
@@ -19913,7 +19909,7 @@
         <v>US7607591002</v>
       </c>
     </row>
-    <row r="368" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
         <v>711</v>
       </c>
@@ -19928,7 +19924,7 @@
         <v>US6826801036</v>
       </c>
     </row>
-    <row r="369" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
         <v>1555</v>
       </c>
@@ -19943,22 +19939,22 @@
         <v>FR0000125007</v>
       </c>
     </row>
-    <row r="370" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
-        <v>2509</v>
+        <v>2507</v>
       </c>
       <c r="B370">
         <v>0.05</v>
       </c>
       <c r="C370" t="s">
-        <v>2444</v>
+        <v>2442</v>
       </c>
       <c r="D370" t="str">
         <f>VLOOKUP(C370,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
         <v>US19260Q1076</v>
       </c>
     </row>
-    <row r="371" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
         <v>1552</v>
       </c>
@@ -19988,7 +19984,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="373" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
         <v>1770</v>
       </c>
@@ -20003,7 +19999,7 @@
         <v>US05722G1004</v>
       </c>
     </row>
-    <row r="374" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
         <v>87</v>
       </c>
@@ -20063,7 +20059,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="378" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
         <v>361</v>
       </c>
@@ -20078,7 +20074,7 @@
         <v>GB00B1YW4409</v>
       </c>
     </row>
-    <row r="379" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
         <v>1568</v>
       </c>
@@ -20108,7 +20104,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="381" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
         <v>519</v>
       </c>
@@ -20116,14 +20112,14 @@
         <v>0.05</v>
       </c>
       <c r="C381" t="s">
-        <v>2451</v>
+        <v>2449</v>
       </c>
       <c r="D381" t="str">
         <f>VLOOKUP(C381,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
         <v>GB00BTK05J60</v>
       </c>
     </row>
-    <row r="382" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
         <v>1067</v>
       </c>
@@ -20155,13 +20151,13 @@
     </row>
     <row r="384" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
-        <v>2510</v>
+        <v>2508</v>
       </c>
       <c r="B384">
         <v>0.05</v>
       </c>
       <c r="C384" t="s">
-        <v>2511</v>
+        <v>2509</v>
       </c>
       <c r="D384" t="e">
         <f>VLOOKUP(C384,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -20183,7 +20179,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="386" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
         <v>1469</v>
       </c>
@@ -20198,7 +20194,7 @@
         <v>US30161N1019</v>
       </c>
     </row>
-    <row r="387" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
         <v>1845</v>
       </c>
@@ -20213,7 +20209,7 @@
         <v>US6098391054</v>
       </c>
     </row>
-    <row r="388" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
         <v>641</v>
       </c>
@@ -20228,9 +20224,9 @@
         <v>JP3733000008</v>
       </c>
     </row>
-    <row r="389" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
-        <v>2512</v>
+        <v>2510</v>
       </c>
       <c r="B389">
         <v>0.05</v>
@@ -20365,13 +20361,13 @@
     </row>
     <row r="398" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
-        <v>2513</v>
+        <v>2511</v>
       </c>
       <c r="B398">
         <v>0.05</v>
       </c>
       <c r="C398" t="s">
-        <v>2514</v>
+        <v>2512</v>
       </c>
       <c r="D398" t="e">
         <f>VLOOKUP(C398,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -20423,7 +20419,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="402" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
         <v>216</v>
       </c>
@@ -20483,7 +20479,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="406" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
         <v>1574</v>
       </c>
@@ -20513,7 +20509,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="408" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
         <v>1520</v>
       </c>
@@ -20528,7 +20524,7 @@
         <v>US7445731067</v>
       </c>
     </row>
-    <row r="409" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
         <v>241</v>
       </c>
@@ -20543,7 +20539,7 @@
         <v>NL0011794037</v>
       </c>
     </row>
-    <row r="410" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
         <v>1073</v>
       </c>
@@ -20573,7 +20569,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="412" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
         <v>1482</v>
       </c>
@@ -20588,9 +20584,9 @@
         <v>US74460D1090</v>
       </c>
     </row>
-    <row r="413" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
-        <v>2515</v>
+        <v>2513</v>
       </c>
       <c r="B413">
         <v>0.05</v>
@@ -20618,7 +20614,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="415" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
         <v>1455</v>
       </c>
@@ -20633,7 +20629,7 @@
         <v>US1924461023</v>
       </c>
     </row>
-    <row r="416" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
         <v>1639</v>
       </c>
@@ -20648,7 +20644,7 @@
         <v>US24703L2025</v>
       </c>
     </row>
-    <row r="417" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
         <v>1059</v>
       </c>
@@ -20663,7 +20659,7 @@
         <v>CA25675T1075</v>
       </c>
     </row>
-    <row r="418" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
         <v>1548</v>
       </c>
@@ -20678,7 +20674,7 @@
         <v>US5010441013</v>
       </c>
     </row>
-    <row r="419" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
         <v>405</v>
       </c>
@@ -20710,7 +20706,7 @@
     </row>
     <row r="421" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
-        <v>2516</v>
+        <v>2514</v>
       </c>
       <c r="B421">
         <v>0.05</v>
@@ -20813,7 +20809,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="428" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
         <v>940</v>
       </c>
@@ -20873,7 +20869,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="432" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
         <v>2308</v>
       </c>
@@ -20948,7 +20944,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="437" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
         <v>783</v>
       </c>
@@ -20963,7 +20959,7 @@
         <v>US8718291078</v>
       </c>
     </row>
-    <row r="438" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
         <v>1782</v>
       </c>
@@ -20980,20 +20976,20 @@
     </row>
     <row r="439" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
-        <v>2517</v>
+        <v>2515</v>
       </c>
       <c r="B439">
         <v>0.04</v>
       </c>
       <c r="C439" t="s">
-        <v>2518</v>
+        <v>2516</v>
       </c>
       <c r="D439" t="e">
         <f>VLOOKUP(C439,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="440" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
         <v>1155</v>
       </c>
@@ -21008,7 +21004,7 @@
         <v>CH0010645932</v>
       </c>
     </row>
-    <row r="441" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
         <v>693</v>
       </c>
@@ -21038,7 +21034,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="443" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
         <v>684</v>
       </c>
@@ -21068,7 +21064,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="445" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
         <v>1564</v>
       </c>
@@ -21113,7 +21109,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="448" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
         <v>127</v>
       </c>
@@ -21158,15 +21154,15 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="451" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
-        <v>2415</v>
+        <v>2413</v>
       </c>
       <c r="B451">
         <v>0.04</v>
       </c>
       <c r="C451" t="s">
-        <v>2414</v>
+        <v>2412</v>
       </c>
       <c r="D451" t="str">
         <f>VLOOKUP(C451,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -21188,7 +21184,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="453" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
         <v>573</v>
       </c>
@@ -21205,7 +21201,7 @@
     </row>
     <row r="454" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
-        <v>2519</v>
+        <v>2517</v>
       </c>
       <c r="B454">
         <v>0.04</v>
@@ -21233,7 +21229,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="456" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
         <v>1604</v>
       </c>
@@ -21263,7 +21259,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="458" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
         <v>1591</v>
       </c>
@@ -21280,20 +21276,20 @@
     </row>
     <row r="459" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
-        <v>2520</v>
+        <v>2518</v>
       </c>
       <c r="B459">
         <v>0.04</v>
       </c>
       <c r="C459" t="s">
-        <v>2521</v>
+        <v>2519</v>
       </c>
       <c r="D459" t="e">
         <f>VLOOKUP(C459,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="460" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
         <v>524</v>
       </c>
@@ -21323,7 +21319,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="462" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
         <v>2374</v>
       </c>
@@ -21340,20 +21336,20 @@
     </row>
     <row r="463" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
-        <v>2522</v>
+        <v>2520</v>
       </c>
       <c r="B463">
         <v>0.04</v>
       </c>
       <c r="C463" t="s">
-        <v>2523</v>
+        <v>2521</v>
       </c>
       <c r="D463" t="e">
         <f>VLOOKUP(C463,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="464" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
         <v>732</v>
       </c>
@@ -21368,7 +21364,7 @@
         <v>AU000000RIO1</v>
       </c>
     </row>
-    <row r="465" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
         <v>1502</v>
       </c>
@@ -21383,7 +21379,7 @@
         <v>US9224751084</v>
       </c>
     </row>
-    <row r="466" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
         <v>1046</v>
       </c>
@@ -21398,7 +21394,7 @@
         <v>US68902V1070</v>
       </c>
     </row>
-    <row r="467" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
         <v>1647</v>
       </c>
@@ -21488,7 +21484,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="473" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
         <v>2337</v>
       </c>
@@ -21533,7 +21529,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="476" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
         <v>1957</v>
       </c>
@@ -21548,7 +21544,7 @@
         <v>US6293775085</v>
       </c>
     </row>
-    <row r="477" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
         <v>299</v>
       </c>
@@ -21580,20 +21576,20 @@
     </row>
     <row r="479" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
-        <v>2524</v>
+        <v>2522</v>
       </c>
       <c r="B479">
         <v>0.04</v>
       </c>
       <c r="C479" t="s">
-        <v>2525</v>
+        <v>2523</v>
       </c>
       <c r="D479" t="e">
         <f>VLOOKUP(C479,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="480" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
         <v>2284</v>
       </c>
@@ -21623,7 +21619,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="482" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
         <v>1704</v>
       </c>
@@ -21640,13 +21636,13 @@
     </row>
     <row r="483" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
-        <v>2526</v>
+        <v>2524</v>
       </c>
       <c r="B483">
         <v>0.04</v>
       </c>
       <c r="C483" t="s">
-        <v>2527</v>
+        <v>2525</v>
       </c>
       <c r="D483" t="e">
         <f>VLOOKUP(C483,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -21670,20 +21666,20 @@
     </row>
     <row r="485" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
-        <v>2528</v>
+        <v>2526</v>
       </c>
       <c r="B485">
         <v>0.04</v>
       </c>
       <c r="C485" t="s">
-        <v>2529</v>
+        <v>2527</v>
       </c>
       <c r="D485" t="e">
         <f>VLOOKUP(C485,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="486" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
         <v>1613</v>
       </c>
@@ -21698,7 +21694,7 @@
         <v>FR0000133308</v>
       </c>
     </row>
-    <row r="487" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
         <v>1961</v>
       </c>
@@ -21713,7 +21709,7 @@
         <v>IL0006046119</v>
       </c>
     </row>
-    <row r="488" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
         <v>617</v>
       </c>
@@ -21728,7 +21724,7 @@
         <v>US87165B1035</v>
       </c>
     </row>
-    <row r="489" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
         <v>1441</v>
       </c>
@@ -21743,7 +21739,7 @@
         <v>US4943681035</v>
       </c>
     </row>
-    <row r="490" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
         <v>1626</v>
       </c>
@@ -21788,7 +21784,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="493" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
         <v>1707</v>
       </c>
@@ -21818,7 +21814,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="495" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
         <v>2288</v>
       </c>
@@ -21833,7 +21829,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="496" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
         <v>838</v>
       </c>
@@ -21850,13 +21846,13 @@
     </row>
     <row r="497" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
-        <v>2530</v>
+        <v>2528</v>
       </c>
       <c r="B497">
         <v>0.04</v>
       </c>
       <c r="C497" t="s">
-        <v>2531</v>
+        <v>2529</v>
       </c>
       <c r="D497" t="e">
         <f>VLOOKUP(C497,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -21908,7 +21904,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="501" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
         <v>958</v>
       </c>
@@ -21940,13 +21936,13 @@
     </row>
     <row r="503" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
-        <v>2532</v>
+        <v>2530</v>
       </c>
       <c r="B503">
         <v>0.04</v>
       </c>
       <c r="C503" t="s">
-        <v>2533</v>
+        <v>2531</v>
       </c>
       <c r="D503" t="e">
         <f>VLOOKUP(C503,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -22013,7 +22009,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="508" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
         <v>2330</v>
       </c>
@@ -22088,7 +22084,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="513" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
         <v>1153</v>
       </c>
@@ -22133,9 +22129,9 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="516" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
-        <v>2400</v>
+        <v>2398</v>
       </c>
       <c r="B516">
         <v>0.04</v>
@@ -22165,13 +22161,13 @@
     </row>
     <row r="518" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
-        <v>2534</v>
+        <v>2532</v>
       </c>
       <c r="B518">
         <v>0.04</v>
       </c>
       <c r="C518" t="s">
-        <v>2535</v>
+        <v>2533</v>
       </c>
       <c r="D518" t="e">
         <f>VLOOKUP(C518,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -22180,13 +22176,13 @@
     </row>
     <row r="519" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
-        <v>2536</v>
+        <v>2534</v>
       </c>
       <c r="B519">
         <v>0.04</v>
       </c>
       <c r="C519" t="s">
-        <v>2537</v>
+        <v>2535</v>
       </c>
       <c r="D519" t="e">
         <f>VLOOKUP(C519,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -22210,7 +22206,7 @@
     </row>
     <row r="521" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
-        <v>2538</v>
+        <v>2536</v>
       </c>
       <c r="B521">
         <v>0.04</v>
@@ -22238,7 +22234,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="523" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
         <v>1741</v>
       </c>
@@ -22253,7 +22249,7 @@
         <v>US7547301090</v>
       </c>
     </row>
-    <row r="524" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
         <v>1727</v>
       </c>
@@ -22298,7 +22294,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="527" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
         <v>1736</v>
       </c>
@@ -22328,7 +22324,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="529" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
         <v>658</v>
       </c>
@@ -22360,20 +22356,20 @@
     </row>
     <row r="531" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
-        <v>2539</v>
+        <v>2537</v>
       </c>
       <c r="B531">
         <v>0.04</v>
       </c>
       <c r="C531" t="s">
-        <v>2540</v>
+        <v>2538</v>
       </c>
       <c r="D531" t="e">
         <f>VLOOKUP(C531,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="532" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
         <v>1834</v>
       </c>
@@ -22390,13 +22386,13 @@
     </row>
     <row r="533" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
-        <v>2541</v>
+        <v>2539</v>
       </c>
       <c r="B533">
         <v>0.04</v>
       </c>
       <c r="C533" t="s">
-        <v>2542</v>
+        <v>2540</v>
       </c>
       <c r="D533" t="e">
         <f>VLOOKUP(C533,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -22405,13 +22401,13 @@
     </row>
     <row r="534" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
-        <v>2543</v>
+        <v>2541</v>
       </c>
       <c r="B534">
         <v>0.04</v>
       </c>
       <c r="C534" t="s">
-        <v>2544</v>
+        <v>2542</v>
       </c>
       <c r="D534" t="e">
         <f>VLOOKUP(C534,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -22435,13 +22431,13 @@
     </row>
     <row r="536" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
-        <v>2545</v>
+        <v>2543</v>
       </c>
       <c r="B536">
         <v>0.03</v>
       </c>
       <c r="C536" t="s">
-        <v>2546</v>
+        <v>2544</v>
       </c>
       <c r="D536" t="e">
         <f>VLOOKUP(C536,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -22463,7 +22459,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="538" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
         <v>746</v>
       </c>
@@ -22480,7 +22476,7 @@
     </row>
     <row r="539" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
-        <v>2547</v>
+        <v>2545</v>
       </c>
       <c r="B539">
         <v>0.03</v>
@@ -22493,7 +22489,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="540" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
         <v>931</v>
       </c>
@@ -22510,13 +22506,13 @@
     </row>
     <row r="541" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
-        <v>2548</v>
+        <v>2546</v>
       </c>
       <c r="B541">
         <v>0.03</v>
       </c>
       <c r="C541" t="s">
-        <v>2549</v>
+        <v>2547</v>
       </c>
       <c r="D541" t="e">
         <f>VLOOKUP(C541,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -22525,13 +22521,13 @@
     </row>
     <row r="542" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
-        <v>2550</v>
+        <v>2548</v>
       </c>
       <c r="B542">
         <v>0.03</v>
       </c>
       <c r="C542" t="s">
-        <v>2551</v>
+        <v>2549</v>
       </c>
       <c r="D542" t="e">
         <f>VLOOKUP(C542,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -22570,20 +22566,20 @@
     </row>
     <row r="545" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A545" t="s">
-        <v>2552</v>
+        <v>2550</v>
       </c>
       <c r="B545">
         <v>0.03</v>
       </c>
       <c r="C545" t="s">
-        <v>2553</v>
+        <v>2551</v>
       </c>
       <c r="D545" t="e">
         <f>VLOOKUP(C545,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="546" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
         <v>2312</v>
       </c>
@@ -22598,7 +22594,7 @@
         <v>US29084Q1004</v>
       </c>
     </row>
-    <row r="547" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
         <v>1765</v>
       </c>
@@ -22628,7 +22624,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="549" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
         <v>2088</v>
       </c>
@@ -22666,14 +22662,14 @@
         <v>0.03</v>
       </c>
       <c r="C551" t="s">
-        <v>2554</v>
+        <v>2552</v>
       </c>
       <c r="D551" t="e">
         <f>VLOOKUP(C551,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="552" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
         <v>1755</v>
       </c>
@@ -22703,7 +22699,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="554" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
         <v>459</v>
       </c>
@@ -22720,13 +22716,13 @@
     </row>
     <row r="555" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
-        <v>2555</v>
+        <v>2553</v>
       </c>
       <c r="B555">
         <v>0.03</v>
       </c>
       <c r="C555" t="s">
-        <v>2556</v>
+        <v>2554</v>
       </c>
       <c r="D555" t="e">
         <f>VLOOKUP(C555,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -22735,13 +22731,13 @@
     </row>
     <row r="556" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A556" t="s">
-        <v>2557</v>
+        <v>2555</v>
       </c>
       <c r="B556">
         <v>0.03</v>
       </c>
       <c r="C556" t="s">
-        <v>2558</v>
+        <v>2556</v>
       </c>
       <c r="D556" t="e">
         <f>VLOOKUP(C556,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -22780,13 +22776,13 @@
     </row>
     <row r="559" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A559" t="s">
-        <v>2559</v>
+        <v>2557</v>
       </c>
       <c r="B559">
         <v>0.03</v>
       </c>
       <c r="C559" t="s">
-        <v>2560</v>
+        <v>2558</v>
       </c>
       <c r="D559" t="e">
         <f>VLOOKUP(C559,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -22840,13 +22836,13 @@
     </row>
     <row r="563" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A563" t="s">
-        <v>2561</v>
+        <v>2559</v>
       </c>
       <c r="B563">
         <v>0.03</v>
       </c>
       <c r="C563" t="s">
-        <v>2562</v>
+        <v>2560</v>
       </c>
       <c r="D563" t="e">
         <f>VLOOKUP(C563,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -22885,13 +22881,13 @@
     </row>
     <row r="566" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
-        <v>2563</v>
+        <v>2561</v>
       </c>
       <c r="B566">
         <v>0.03</v>
       </c>
       <c r="C566" t="s">
-        <v>2564</v>
+        <v>2562</v>
       </c>
       <c r="D566" t="e">
         <f>VLOOKUP(C566,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -22900,13 +22896,13 @@
     </row>
     <row r="567" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
-        <v>2565</v>
+        <v>2563</v>
       </c>
       <c r="B567">
         <v>0.03</v>
       </c>
       <c r="C567" t="s">
-        <v>2566</v>
+        <v>2564</v>
       </c>
       <c r="D567" t="e">
         <f>VLOOKUP(C567,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -22928,7 +22924,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="569" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
         <v>1715</v>
       </c>
@@ -22945,13 +22941,13 @@
     </row>
     <row r="570" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A570" t="s">
-        <v>2567</v>
+        <v>2565</v>
       </c>
       <c r="B570">
         <v>0.03</v>
       </c>
       <c r="C570" t="s">
-        <v>2568</v>
+        <v>2566</v>
       </c>
       <c r="D570" t="e">
         <f>VLOOKUP(C570,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -23003,7 +22999,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="574" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A574" t="s">
         <v>1481</v>
       </c>
@@ -23018,7 +23014,7 @@
         <v>SE0000108656</v>
       </c>
     </row>
-    <row r="575" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
         <v>1588</v>
       </c>
@@ -23063,15 +23059,15 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="578" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A578" t="s">
-        <v>2569</v>
+        <v>2567</v>
       </c>
       <c r="B578">
         <v>0.03</v>
       </c>
       <c r="C578" t="s">
-        <v>2401</v>
+        <v>2399</v>
       </c>
       <c r="D578" t="str">
         <f>VLOOKUP(C578,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -23086,7 +23082,7 @@
         <v>0.03</v>
       </c>
       <c r="C579" t="s">
-        <v>2570</v>
+        <v>2568</v>
       </c>
       <c r="D579" t="e">
         <f>VLOOKUP(C579,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -23110,20 +23106,20 @@
     </row>
     <row r="581" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A581" t="s">
-        <v>2571</v>
+        <v>2569</v>
       </c>
       <c r="B581">
         <v>0.03</v>
       </c>
       <c r="C581" t="s">
-        <v>2572</v>
+        <v>2570</v>
       </c>
       <c r="D581" t="e">
         <f>VLOOKUP(C581,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="582" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A582" t="s">
         <v>1016</v>
       </c>
@@ -23153,7 +23149,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="584" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A584" t="s">
         <v>1581</v>
       </c>
@@ -23168,7 +23164,7 @@
         <v>US0534841012</v>
       </c>
     </row>
-    <row r="585" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A585" t="s">
         <v>479</v>
       </c>
@@ -23228,7 +23224,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="589" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A589" t="s">
         <v>2345</v>
       </c>
@@ -23258,7 +23254,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="591" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A591" t="s">
         <v>1570</v>
       </c>
@@ -23348,7 +23344,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="597" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A597" t="s">
         <v>551</v>
       </c>
@@ -23438,7 +23434,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="603" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A603" t="s">
         <v>2315</v>
       </c>
@@ -23455,13 +23451,13 @@
     </row>
     <row r="604" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A604" t="s">
-        <v>2573</v>
+        <v>2571</v>
       </c>
       <c r="B604">
         <v>0.03</v>
       </c>
       <c r="C604" t="s">
-        <v>2574</v>
+        <v>2572</v>
       </c>
       <c r="D604" t="e">
         <f>VLOOKUP(C604,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -23498,7 +23494,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="607" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A607" t="s">
         <v>1257</v>
       </c>
@@ -23558,7 +23554,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="611" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A611" t="s">
         <v>835</v>
       </c>
@@ -23620,20 +23616,20 @@
     </row>
     <row r="615" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A615" t="s">
-        <v>2575</v>
+        <v>2573</v>
       </c>
       <c r="B615">
         <v>0.03</v>
       </c>
       <c r="C615" t="s">
-        <v>2576</v>
+        <v>2574</v>
       </c>
       <c r="D615" t="e">
         <f>VLOOKUP(C615,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="616" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A616" t="s">
         <v>832</v>
       </c>
@@ -23725,20 +23721,20 @@
     </row>
     <row r="622" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A622" t="s">
-        <v>2577</v>
+        <v>2575</v>
       </c>
       <c r="B622">
         <v>0.03</v>
       </c>
       <c r="C622" t="s">
-        <v>2578</v>
+        <v>2576</v>
       </c>
       <c r="D622" t="e">
         <f>VLOOKUP(C622,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="623" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A623" t="s">
         <v>1719</v>
       </c>
@@ -23798,7 +23794,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="627" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A627" t="s">
         <v>1282</v>
       </c>
@@ -23828,9 +23824,9 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="629" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A629" t="s">
-        <v>2579</v>
+        <v>2577</v>
       </c>
       <c r="B629">
         <v>0.03</v>
@@ -23858,7 +23854,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="631" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A631" t="s">
         <v>785</v>
       </c>
@@ -23873,7 +23869,7 @@
         <v>US5500211090</v>
       </c>
     </row>
-    <row r="632" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A632" t="s">
         <v>1683</v>
       </c>
@@ -23888,9 +23884,9 @@
         <v>US4062161017</v>
       </c>
     </row>
-    <row r="633" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A633" t="s">
-        <v>2580</v>
+        <v>2578</v>
       </c>
       <c r="B633">
         <v>0.03</v>
@@ -23918,7 +23914,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="635" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A635" t="s">
         <v>1148</v>
       </c>
@@ -23965,13 +23961,13 @@
     </row>
     <row r="638" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A638" t="s">
-        <v>2581</v>
+        <v>2579</v>
       </c>
       <c r="B638">
         <v>0.03</v>
       </c>
       <c r="C638" t="s">
-        <v>2582</v>
+        <v>2580</v>
       </c>
       <c r="D638" t="e">
         <f>VLOOKUP(C638,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -24040,20 +24036,20 @@
     </row>
     <row r="643" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A643" t="s">
-        <v>2583</v>
+        <v>2581</v>
       </c>
       <c r="B643">
         <v>0.03</v>
       </c>
       <c r="C643" t="s">
-        <v>2584</v>
+        <v>2582</v>
       </c>
       <c r="D643" t="e">
         <f>VLOOKUP(C643,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="644" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A644" t="s">
         <v>996</v>
       </c>
@@ -24068,7 +24064,7 @@
         <v>US2810201077</v>
       </c>
     </row>
-    <row r="645" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A645" t="s">
         <v>421</v>
       </c>
@@ -24100,13 +24096,13 @@
     </row>
     <row r="647" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A647" t="s">
-        <v>2585</v>
+        <v>2583</v>
       </c>
       <c r="B647">
         <v>0.03</v>
       </c>
       <c r="C647" t="s">
-        <v>2586</v>
+        <v>2584</v>
       </c>
       <c r="D647" t="e">
         <f>VLOOKUP(C647,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -24115,13 +24111,13 @@
     </row>
     <row r="648" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A648" t="s">
-        <v>2587</v>
+        <v>2585</v>
       </c>
       <c r="B648">
         <v>0.03</v>
       </c>
       <c r="C648" t="s">
-        <v>2588</v>
+        <v>2586</v>
       </c>
       <c r="D648" t="e">
         <f>VLOOKUP(C648,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -24143,7 +24139,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="650" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A650" t="s">
         <v>1439</v>
       </c>
@@ -24181,7 +24177,7 @@
         <v>0.03</v>
       </c>
       <c r="C652" t="s">
-        <v>2589</v>
+        <v>2587</v>
       </c>
       <c r="D652" t="e">
         <f>VLOOKUP(C652,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -24190,13 +24186,13 @@
     </row>
     <row r="653" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A653" t="s">
-        <v>2590</v>
+        <v>2588</v>
       </c>
       <c r="B653">
         <v>0.03</v>
       </c>
       <c r="C653" t="s">
-        <v>2591</v>
+        <v>2589</v>
       </c>
       <c r="D653" t="e">
         <f>VLOOKUP(C653,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -24235,20 +24231,20 @@
     </row>
     <row r="656" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A656" t="s">
-        <v>2592</v>
+        <v>2590</v>
       </c>
       <c r="B656">
         <v>0.03</v>
       </c>
       <c r="C656" t="s">
-        <v>2593</v>
+        <v>2591</v>
       </c>
       <c r="D656" t="e">
         <f>VLOOKUP(C656,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="657" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A657" t="s">
         <v>1566</v>
       </c>
@@ -24263,7 +24259,7 @@
         <v>US29476L1070</v>
       </c>
     </row>
-    <row r="658" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A658" t="s">
         <v>1881</v>
       </c>
@@ -24295,13 +24291,13 @@
     </row>
     <row r="660" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A660" t="s">
-        <v>2594</v>
+        <v>2592</v>
       </c>
       <c r="B660">
         <v>0.03</v>
       </c>
       <c r="C660" t="s">
-        <v>2595</v>
+        <v>2593</v>
       </c>
       <c r="D660" t="e">
         <f>VLOOKUP(C660,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -24383,7 +24379,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="666" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A666" t="s">
         <v>1943</v>
       </c>
@@ -24445,20 +24441,20 @@
     </row>
     <row r="670" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A670" t="s">
-        <v>2596</v>
+        <v>2594</v>
       </c>
       <c r="B670">
         <v>0.03</v>
       </c>
       <c r="C670" t="s">
-        <v>2597</v>
+        <v>2595</v>
       </c>
       <c r="D670" t="e">
         <f>VLOOKUP(C670,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="671" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A671" t="s">
         <v>322</v>
       </c>
@@ -24503,7 +24499,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="674" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A674" t="s">
         <v>1749</v>
       </c>
@@ -24518,7 +24514,7 @@
         <v>CA7063271034</v>
       </c>
     </row>
-    <row r="675" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A675" t="s">
         <v>933</v>
       </c>
@@ -24550,20 +24546,20 @@
     </row>
     <row r="677" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A677" t="s">
-        <v>2598</v>
+        <v>2596</v>
       </c>
       <c r="B677">
         <v>0.03</v>
       </c>
       <c r="C677" t="s">
-        <v>2599</v>
+        <v>2597</v>
       </c>
       <c r="D677" t="e">
         <f>VLOOKUP(C677,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="678" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A678" t="s">
         <v>888</v>
       </c>
@@ -24578,7 +24574,7 @@
         <v>US2371941053</v>
       </c>
     </row>
-    <row r="679" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A679" t="s">
         <v>808</v>
       </c>
@@ -24593,9 +24589,9 @@
         <v>FR0000045072</v>
       </c>
     </row>
-    <row r="680" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A680" t="s">
-        <v>2600</v>
+        <v>2598</v>
       </c>
       <c r="B680">
         <v>0.03</v>
@@ -24608,7 +24604,7 @@
         <v>US9699041011</v>
       </c>
     </row>
-    <row r="681" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A681" t="s">
         <v>2370</v>
       </c>
@@ -24625,13 +24621,13 @@
     </row>
     <row r="682" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A682" t="s">
-        <v>2601</v>
+        <v>2599</v>
       </c>
       <c r="B682">
         <v>0.03</v>
       </c>
       <c r="C682" t="s">
-        <v>2602</v>
+        <v>2600</v>
       </c>
       <c r="D682" t="e">
         <f>VLOOKUP(C682,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -24728,9 +24724,9 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="689" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A689" t="s">
-        <v>2603</v>
+        <v>2601</v>
       </c>
       <c r="B689">
         <v>0.03</v>
@@ -24743,7 +24739,7 @@
         <v>GB00BDCPN049</v>
       </c>
     </row>
-    <row r="690" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A690" t="s">
         <v>1577</v>
       </c>
@@ -24758,7 +24754,7 @@
         <v>FR001400AJ45</v>
       </c>
     </row>
-    <row r="691" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A691" t="s">
         <v>1705</v>
       </c>
@@ -24773,7 +24769,7 @@
         <v>DE0005785604</v>
       </c>
     </row>
-    <row r="692" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A692" t="s">
         <v>645</v>
       </c>
@@ -24803,7 +24799,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="694" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A694" t="s">
         <v>1966</v>
       </c>
@@ -24820,20 +24816,20 @@
     </row>
     <row r="695" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A695" t="s">
-        <v>2604</v>
+        <v>2602</v>
       </c>
       <c r="B695">
         <v>0.02</v>
       </c>
       <c r="C695" t="s">
-        <v>2605</v>
+        <v>2603</v>
       </c>
       <c r="D695" t="e">
         <f>VLOOKUP(C695,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="696" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A696" t="s">
         <v>1720</v>
       </c>
@@ -24850,7 +24846,7 @@
     </row>
     <row r="697" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A697" t="s">
-        <v>2606</v>
+        <v>2604</v>
       </c>
       <c r="B697">
         <v>0.02</v>
@@ -24878,7 +24874,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="699" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A699" t="s">
         <v>643</v>
       </c>
@@ -24910,13 +24906,13 @@
     </row>
     <row r="701" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A701" t="s">
-        <v>2607</v>
+        <v>2605</v>
       </c>
       <c r="B701">
         <v>0.02</v>
       </c>
       <c r="C701" t="s">
-        <v>2608</v>
+        <v>2606</v>
       </c>
       <c r="D701" t="e">
         <f>VLOOKUP(C701,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -24940,13 +24936,13 @@
     </row>
     <row r="703" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A703" t="s">
-        <v>2609</v>
+        <v>2607</v>
       </c>
       <c r="B703">
         <v>0.02</v>
       </c>
       <c r="C703" t="s">
-        <v>2610</v>
+        <v>2608</v>
       </c>
       <c r="D703" t="e">
         <f>VLOOKUP(C703,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -24968,7 +24964,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="705" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A705" t="s">
         <v>898</v>
       </c>
@@ -24983,7 +24979,7 @@
         <v>US92343E1029</v>
       </c>
     </row>
-    <row r="706" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A706" t="s">
         <v>399</v>
       </c>
@@ -24998,7 +24994,7 @@
         <v>NL0010773842</v>
       </c>
     </row>
-    <row r="707" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A707" t="s">
         <v>2198</v>
       </c>
@@ -25013,9 +25009,9 @@
         <v>NL0011540547</v>
       </c>
     </row>
-    <row r="708" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A708" t="s">
-        <v>2611</v>
+        <v>2609</v>
       </c>
       <c r="B708">
         <v>0.02</v>
@@ -25043,7 +25039,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="710" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A710" t="s">
         <v>1659</v>
       </c>
@@ -25088,7 +25084,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="713" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A713" t="s">
         <v>1665</v>
       </c>
@@ -25118,7 +25114,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="715" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A715" t="s">
         <v>1601</v>
       </c>
@@ -25156,14 +25152,14 @@
         <v>0.02</v>
       </c>
       <c r="C717" t="s">
-        <v>2612</v>
+        <v>2610</v>
       </c>
       <c r="D717" t="e">
         <f>VLOOKUP(C717,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="718" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A718" t="s">
         <v>1904</v>
       </c>
@@ -25178,7 +25174,7 @@
         <v>AU000000BXB1</v>
       </c>
     </row>
-    <row r="719" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A719" t="s">
         <v>2365</v>
       </c>
@@ -25210,20 +25206,20 @@
     </row>
     <row r="721" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A721" t="s">
-        <v>2613</v>
+        <v>2611</v>
       </c>
       <c r="B721">
         <v>0.02</v>
       </c>
       <c r="C721" t="s">
-        <v>2614</v>
+        <v>2612</v>
       </c>
       <c r="D721" t="e">
         <f>VLOOKUP(C721,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="722" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A722" t="s">
         <v>810</v>
       </c>
@@ -25240,13 +25236,13 @@
     </row>
     <row r="723" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A723" t="s">
-        <v>2615</v>
+        <v>2613</v>
       </c>
       <c r="B723">
         <v>0.02</v>
       </c>
       <c r="C723" t="s">
-        <v>2616</v>
+        <v>2614</v>
       </c>
       <c r="D723" t="e">
         <f>VLOOKUP(C723,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -25343,7 +25339,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="730" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A730" t="s">
         <v>416</v>
       </c>
@@ -25358,7 +25354,7 @@
         <v>US74834L1008</v>
       </c>
     </row>
-    <row r="731" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A731" t="s">
         <v>771</v>
       </c>
@@ -25373,7 +25369,7 @@
         <v>US4435731009</v>
       </c>
     </row>
-    <row r="732" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A732" t="s">
         <v>1740</v>
       </c>
@@ -25405,13 +25401,13 @@
     </row>
     <row r="734" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A734" t="s">
-        <v>2617</v>
+        <v>2615</v>
       </c>
       <c r="B734">
         <v>0.02</v>
       </c>
       <c r="C734" t="s">
-        <v>2618</v>
+        <v>2616</v>
       </c>
       <c r="D734" t="e">
         <f>VLOOKUP(C734,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -25480,7 +25476,7 @@
     </row>
     <row r="739" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A739" t="s">
-        <v>2619</v>
+        <v>2617</v>
       </c>
       <c r="B739">
         <v>0.02</v>
@@ -25493,7 +25489,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="740" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A740" t="s">
         <v>1827</v>
       </c>
@@ -25508,7 +25504,7 @@
         <v>US35137L1052</v>
       </c>
     </row>
-    <row r="741" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A741" t="s">
         <v>1641</v>
       </c>
@@ -25525,13 +25521,13 @@
     </row>
     <row r="742" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A742" t="s">
-        <v>2620</v>
+        <v>2618</v>
       </c>
       <c r="B742">
         <v>0.02</v>
       </c>
       <c r="C742" t="s">
-        <v>2621</v>
+        <v>2619</v>
       </c>
       <c r="D742" t="e">
         <f>VLOOKUP(C742,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -25540,35 +25536,35 @@
     </row>
     <row r="743" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A743" t="s">
-        <v>2622</v>
+        <v>2620</v>
       </c>
       <c r="B743">
         <v>0.02</v>
       </c>
       <c r="C743" t="s">
-        <v>2623</v>
+        <v>2621</v>
       </c>
       <c r="D743" t="e">
         <f>VLOOKUP(C743,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="744" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A744" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="B744">
         <v>0.02</v>
       </c>
       <c r="C744" t="s">
-        <v>2404</v>
+        <v>2402</v>
       </c>
       <c r="D744" t="str">
         <f>VLOOKUP(C744,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
         <v>IE00BD1RP616</v>
       </c>
     </row>
-    <row r="745" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A745" t="s">
         <v>2079</v>
       </c>
@@ -25628,7 +25624,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="749" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A749" t="s">
         <v>1549</v>
       </c>
@@ -25703,7 +25699,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="754" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A754" t="s">
         <v>589</v>
       </c>
@@ -25748,7 +25744,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="757" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A757" t="s">
         <v>1862</v>
       </c>
@@ -25823,7 +25819,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="762" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A762" t="s">
         <v>1014</v>
       </c>
@@ -25883,7 +25879,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="766" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A766" t="s">
         <v>1573</v>
       </c>
@@ -25898,7 +25894,7 @@
         <v>HK0669013440</v>
       </c>
     </row>
-    <row r="767" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A767" t="s">
         <v>1128</v>
       </c>
@@ -25913,7 +25909,7 @@
         <v>US6951561090</v>
       </c>
     </row>
-    <row r="768" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A768" t="s">
         <v>1110</v>
       </c>
@@ -25928,15 +25924,15 @@
         <v>AU0000030678</v>
       </c>
     </row>
-    <row r="769" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A769" t="s">
-        <v>2434</v>
+        <v>2432</v>
       </c>
       <c r="B769">
         <v>0.02</v>
       </c>
       <c r="C769" t="s">
-        <v>2433</v>
+        <v>2431</v>
       </c>
       <c r="D769" t="str">
         <f>VLOOKUP(C769,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -25960,7 +25956,7 @@
     </row>
     <row r="771" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A771" t="s">
-        <v>2624</v>
+        <v>2622</v>
       </c>
       <c r="B771">
         <v>0.02</v>
@@ -26018,7 +26014,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="775" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A775" t="s">
         <v>1746</v>
       </c>
@@ -26080,20 +26076,20 @@
     </row>
     <row r="779" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A779" t="s">
-        <v>2625</v>
+        <v>2623</v>
       </c>
       <c r="B779">
         <v>0.02</v>
       </c>
       <c r="C779" t="s">
-        <v>2626</v>
+        <v>2624</v>
       </c>
       <c r="D779" t="e">
         <f>VLOOKUP(C779,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="780" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A780" t="s">
         <v>1896</v>
       </c>
@@ -26123,7 +26119,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="782" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A782" t="s">
         <v>1603</v>
       </c>
@@ -26155,13 +26151,13 @@
     </row>
     <row r="784" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A784" t="s">
-        <v>2627</v>
+        <v>2625</v>
       </c>
       <c r="B784">
         <v>0.02</v>
       </c>
       <c r="C784" t="s">
-        <v>2628</v>
+        <v>2626</v>
       </c>
       <c r="D784" t="e">
         <f>VLOOKUP(C784,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -26183,7 +26179,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="786" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A786" t="s">
         <v>1848</v>
       </c>
@@ -26200,13 +26196,13 @@
     </row>
     <row r="787" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A787" t="s">
-        <v>2629</v>
+        <v>2627</v>
       </c>
       <c r="B787">
         <v>0.02</v>
       </c>
       <c r="C787" t="s">
-        <v>2630</v>
+        <v>2628</v>
       </c>
       <c r="D787" t="e">
         <f>VLOOKUP(C787,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -26221,14 +26217,14 @@
         <v>0.02</v>
       </c>
       <c r="C788" t="s">
-        <v>2631</v>
+        <v>2629</v>
       </c>
       <c r="D788" t="e">
         <f>VLOOKUP(C788,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="789" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="789" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A789" t="s">
         <v>397</v>
       </c>
@@ -26245,13 +26241,13 @@
     </row>
     <row r="790" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A790" t="s">
-        <v>2632</v>
+        <v>2630</v>
       </c>
       <c r="B790">
         <v>0.02</v>
       </c>
       <c r="C790" t="s">
-        <v>2633</v>
+        <v>2631</v>
       </c>
       <c r="D790" t="e">
         <f>VLOOKUP(C790,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -26260,13 +26256,13 @@
     </row>
     <row r="791" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A791" t="s">
-        <v>2634</v>
+        <v>2632</v>
       </c>
       <c r="B791">
         <v>0.02</v>
       </c>
       <c r="C791" t="s">
-        <v>2635</v>
+        <v>2633</v>
       </c>
       <c r="D791" t="e">
         <f>VLOOKUP(C791,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -26311,14 +26307,14 @@
         <v>0.02</v>
       </c>
       <c r="C794" t="s">
-        <v>2636</v>
+        <v>2634</v>
       </c>
       <c r="D794" t="e">
         <f>VLOOKUP(C794,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="795" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="795" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A795" t="s">
         <v>1289</v>
       </c>
@@ -26348,7 +26344,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="797" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="797" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A797" t="s">
         <v>1799</v>
       </c>
@@ -26380,13 +26376,13 @@
     </row>
     <row r="799" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A799" t="s">
-        <v>2637</v>
+        <v>2635</v>
       </c>
       <c r="B799">
         <v>0.02</v>
       </c>
       <c r="C799" t="s">
-        <v>2638</v>
+        <v>2636</v>
       </c>
       <c r="D799" t="e">
         <f>VLOOKUP(C799,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -26395,13 +26391,13 @@
     </row>
     <row r="800" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A800" t="s">
-        <v>2639</v>
+        <v>2637</v>
       </c>
       <c r="B800">
         <v>0.02</v>
       </c>
       <c r="C800" t="s">
-        <v>2640</v>
+        <v>2638</v>
       </c>
       <c r="D800" t="e">
         <f>VLOOKUP(C800,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -26438,7 +26434,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="803" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="803" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A803" t="s">
         <v>1685</v>
       </c>
@@ -26536,7 +26532,7 @@
         <v>0.02</v>
       </c>
       <c r="C809" t="s">
-        <v>2641</v>
+        <v>2639</v>
       </c>
       <c r="D809" t="e">
         <f>VLOOKUP(C809,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -26605,13 +26601,13 @@
     </row>
     <row r="814" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A814" t="s">
-        <v>2642</v>
+        <v>2640</v>
       </c>
       <c r="B814">
         <v>0.02</v>
       </c>
       <c r="C814" t="s">
-        <v>2643</v>
+        <v>2641</v>
       </c>
       <c r="D814" t="e">
         <f>VLOOKUP(C814,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -26693,7 +26689,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="820" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="820" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A820" t="s">
         <v>663</v>
       </c>
@@ -26701,7 +26697,7 @@
         <v>0.02</v>
       </c>
       <c r="C820" t="s">
-        <v>2446</v>
+        <v>2444</v>
       </c>
       <c r="D820" t="str">
         <f>VLOOKUP(C820,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -26755,13 +26751,13 @@
     </row>
     <row r="824" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A824" t="s">
-        <v>2644</v>
+        <v>2642</v>
       </c>
       <c r="B824">
         <v>0.02</v>
       </c>
       <c r="C824" t="s">
-        <v>2645</v>
+        <v>2643</v>
       </c>
       <c r="D824" t="e">
         <f>VLOOKUP(C824,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -26798,7 +26794,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="827" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="827" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A827" t="s">
         <v>567</v>
       </c>
@@ -26828,7 +26824,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="829" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="829" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A829" t="s">
         <v>1823</v>
       </c>
@@ -26845,13 +26841,13 @@
     </row>
     <row r="830" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A830" t="s">
-        <v>2646</v>
+        <v>2644</v>
       </c>
       <c r="B830">
         <v>0.02</v>
       </c>
       <c r="C830" t="s">
-        <v>2647</v>
+        <v>2645</v>
       </c>
       <c r="D830" t="e">
         <f>VLOOKUP(C830,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -26860,13 +26856,13 @@
     </row>
     <row r="831" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A831" t="s">
-        <v>2648</v>
+        <v>2646</v>
       </c>
       <c r="B831">
         <v>0.02</v>
       </c>
       <c r="C831" t="s">
-        <v>2649</v>
+        <v>2647</v>
       </c>
       <c r="D831" t="e">
         <f>VLOOKUP(C831,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -26888,15 +26884,15 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="833" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="833" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A833" t="s">
-        <v>2650</v>
+        <v>2648</v>
       </c>
       <c r="B833">
         <v>0.02</v>
       </c>
       <c r="C833" t="s">
-        <v>2427</v>
+        <v>2425</v>
       </c>
       <c r="D833" t="str">
         <f>VLOOKUP(C833,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -26948,7 +26944,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="837" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="837" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A837" t="s">
         <v>2341</v>
       </c>
@@ -27040,22 +27036,22 @@
     </row>
     <row r="843" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A843" t="s">
-        <v>2651</v>
+        <v>2649</v>
       </c>
       <c r="B843">
         <v>0.02</v>
       </c>
       <c r="C843" t="s">
-        <v>2652</v>
+        <v>2650</v>
       </c>
       <c r="D843" t="e">
         <f>VLOOKUP(C843,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="844" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="844" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A844" t="s">
-        <v>2653</v>
+        <v>2651</v>
       </c>
       <c r="B844">
         <v>0.02</v>
@@ -27083,7 +27079,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="846" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="846" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A846" t="s">
         <v>2355</v>
       </c>
@@ -27113,7 +27109,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="848" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="848" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A848" t="s">
         <v>1722</v>
       </c>
@@ -27130,20 +27126,20 @@
     </row>
     <row r="849" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A849" t="s">
-        <v>2654</v>
+        <v>2652</v>
       </c>
       <c r="B849">
         <v>0.02</v>
       </c>
       <c r="C849" t="s">
-        <v>2655</v>
+        <v>2653</v>
       </c>
       <c r="D849" t="e">
         <f>VLOOKUP(C849,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="850" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="850" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A850" t="s">
         <v>2320</v>
       </c>
@@ -27175,13 +27171,13 @@
     </row>
     <row r="852" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A852" t="s">
-        <v>2656</v>
+        <v>2654</v>
       </c>
       <c r="B852">
         <v>0.02</v>
       </c>
       <c r="C852" t="s">
-        <v>2657</v>
+        <v>2655</v>
       </c>
       <c r="D852" t="e">
         <f>VLOOKUP(C852,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -27203,7 +27199,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="854" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="854" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A854" t="s">
         <v>1480</v>
       </c>
@@ -27265,13 +27261,13 @@
     </row>
     <row r="858" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A858" t="s">
-        <v>2658</v>
+        <v>2656</v>
       </c>
       <c r="B858">
         <v>0.02</v>
       </c>
       <c r="C858" t="s">
-        <v>2659</v>
+        <v>2657</v>
       </c>
       <c r="D858" t="e">
         <f>VLOOKUP(C858,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -27323,7 +27319,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="862" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="862" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A862" t="s">
         <v>2094</v>
       </c>
@@ -27368,7 +27364,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="865" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="865" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A865" t="s">
         <v>1632</v>
       </c>
@@ -27383,7 +27379,7 @@
         <v>DE0006048432</v>
       </c>
     </row>
-    <row r="866" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="866" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A866" t="s">
         <v>1858</v>
       </c>
@@ -27398,7 +27394,7 @@
         <v>NZFAPE0001S2</v>
       </c>
     </row>
-    <row r="867" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="867" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A867" t="s">
         <v>1923</v>
       </c>
@@ -27406,14 +27402,14 @@
         <v>0.02</v>
       </c>
       <c r="C867" t="s">
-        <v>2453</v>
+        <v>2451</v>
       </c>
       <c r="D867" t="str">
         <f>VLOOKUP(C867,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
         <v>US0357108390</v>
       </c>
     </row>
-    <row r="868" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="868" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A868" t="s">
         <v>1695</v>
       </c>
@@ -27428,7 +27424,7 @@
         <v>JP3347200002</v>
       </c>
     </row>
-    <row r="869" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="869" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A869" t="s">
         <v>1871</v>
       </c>
@@ -27475,7 +27471,7 @@
     </row>
     <row r="872" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A872" t="s">
-        <v>2660</v>
+        <v>2658</v>
       </c>
       <c r="B872">
         <v>0.02</v>
@@ -27578,7 +27574,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="879" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="879" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A879" t="s">
         <v>2332</v>
       </c>
@@ -27593,7 +27589,7 @@
         <v>JP3118000003</v>
       </c>
     </row>
-    <row r="880" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="880" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A880" t="s">
         <v>1806</v>
       </c>
@@ -27631,7 +27627,7 @@
         <v>0.02</v>
       </c>
       <c r="C882" t="s">
-        <v>2661</v>
+        <v>2659</v>
       </c>
       <c r="D882" t="e">
         <f>VLOOKUP(C882,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -27653,7 +27649,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="884" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="884" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A884" t="s">
         <v>2108</v>
       </c>
@@ -27683,7 +27679,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="886" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="886" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A886" t="s">
         <v>729</v>
       </c>
@@ -27713,7 +27709,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="888" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="888" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A888" t="s">
         <v>1887</v>
       </c>
@@ -27758,7 +27754,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="891" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="891" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A891" t="s">
         <v>2034</v>
       </c>
@@ -27803,7 +27799,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="894" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="894" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A894" t="s">
         <v>1924</v>
       </c>
@@ -27818,7 +27814,7 @@
         <v>US9139031002</v>
       </c>
     </row>
-    <row r="895" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="895" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A895" t="s">
         <v>2091</v>
       </c>
@@ -27848,7 +27844,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="897" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="897" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A897" t="s">
         <v>1198</v>
       </c>
@@ -27863,7 +27859,7 @@
         <v>US1252691001</v>
       </c>
     </row>
-    <row r="898" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="898" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A898" t="s">
         <v>2028</v>
       </c>
@@ -27878,7 +27874,7 @@
         <v>AU000000SUN6</v>
       </c>
     </row>
-    <row r="899" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="899" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A899" t="s">
         <v>1861</v>
       </c>
@@ -27895,13 +27891,13 @@
     </row>
     <row r="900" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A900" t="s">
-        <v>2662</v>
+        <v>2660</v>
       </c>
       <c r="B900">
         <v>0.02</v>
       </c>
       <c r="C900" t="s">
-        <v>2663</v>
+        <v>2661</v>
       </c>
       <c r="D900" t="e">
         <f>VLOOKUP(C900,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -27923,7 +27919,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="902" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="902" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A902" t="s">
         <v>1900</v>
       </c>
@@ -27938,7 +27934,7 @@
         <v>IE00BFRT3W74</v>
       </c>
     </row>
-    <row r="903" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="903" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A903" t="s">
         <v>2044</v>
       </c>
@@ -27953,7 +27949,7 @@
         <v>CH0198251305</v>
       </c>
     </row>
-    <row r="904" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="904" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A904" t="s">
         <v>1873</v>
       </c>
@@ -27985,13 +27981,13 @@
     </row>
     <row r="906" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A906" t="s">
-        <v>2664</v>
+        <v>2662</v>
       </c>
       <c r="B906">
         <v>0.02</v>
       </c>
       <c r="C906" t="s">
-        <v>2665</v>
+        <v>2663</v>
       </c>
       <c r="D906" t="e">
         <f>VLOOKUP(C906,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -28000,7 +27996,7 @@
     </row>
     <row r="907" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A907" t="s">
-        <v>2666</v>
+        <v>2664</v>
       </c>
       <c r="B907">
         <v>0.02</v>
@@ -28015,13 +28011,13 @@
     </row>
     <row r="908" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A908" t="s">
-        <v>2667</v>
+        <v>2665</v>
       </c>
       <c r="B908">
         <v>0.02</v>
       </c>
       <c r="C908" t="s">
-        <v>2668</v>
+        <v>2666</v>
       </c>
       <c r="D908" t="e">
         <f>VLOOKUP(C908,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -28043,7 +28039,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="910" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="910" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A910" t="s">
         <v>2110</v>
       </c>
@@ -28058,7 +28054,7 @@
         <v>CA5503721063</v>
       </c>
     </row>
-    <row r="911" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="911" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A911" t="s">
         <v>1554</v>
       </c>
@@ -28075,13 +28071,13 @@
     </row>
     <row r="912" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A912" t="s">
-        <v>2669</v>
+        <v>2667</v>
       </c>
       <c r="B912">
         <v>0.02</v>
       </c>
       <c r="C912" t="s">
-        <v>2670</v>
+        <v>2668</v>
       </c>
       <c r="D912" t="e">
         <f>VLOOKUP(C912,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -28090,13 +28086,13 @@
     </row>
     <row r="913" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A913" t="s">
-        <v>2671</v>
+        <v>2669</v>
       </c>
       <c r="B913">
         <v>0.02</v>
       </c>
       <c r="C913" t="s">
-        <v>2672</v>
+        <v>2670</v>
       </c>
       <c r="D913" t="e">
         <f>VLOOKUP(C913,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -28105,13 +28101,13 @@
     </row>
     <row r="914" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A914" t="s">
-        <v>2673</v>
+        <v>2671</v>
       </c>
       <c r="B914">
         <v>0.02</v>
       </c>
       <c r="C914" t="s">
-        <v>2674</v>
+        <v>2672</v>
       </c>
       <c r="D914" t="e">
         <f>VLOOKUP(C914,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -28133,7 +28129,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="916" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="916" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A916" t="s">
         <v>890</v>
       </c>
@@ -28165,13 +28161,13 @@
     </row>
     <row r="918" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A918" t="s">
-        <v>2675</v>
+        <v>2673</v>
       </c>
       <c r="B918">
         <v>0.02</v>
       </c>
       <c r="C918" t="s">
-        <v>2676</v>
+        <v>2674</v>
       </c>
       <c r="D918" t="e">
         <f>VLOOKUP(C918,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -28186,7 +28182,7 @@
         <v>0.02</v>
       </c>
       <c r="C919" t="s">
-        <v>2677</v>
+        <v>2675</v>
       </c>
       <c r="D919" t="e">
         <f>VLOOKUP(C919,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -28208,7 +28204,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="921" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="921" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A921" t="s">
         <v>743</v>
       </c>
@@ -28270,20 +28266,20 @@
     </row>
     <row r="925" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A925" t="s">
-        <v>2678</v>
+        <v>2676</v>
       </c>
       <c r="B925">
         <v>0.02</v>
       </c>
       <c r="C925" t="s">
-        <v>2679</v>
+        <v>2677</v>
       </c>
       <c r="D925" t="e">
         <f>VLOOKUP(C925,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="926" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="926" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A926" t="s">
         <v>1992</v>
       </c>
@@ -28300,20 +28296,20 @@
     </row>
     <row r="927" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A927" t="s">
-        <v>2680</v>
+        <v>2678</v>
       </c>
       <c r="B927">
         <v>0.02</v>
       </c>
       <c r="C927" t="s">
-        <v>2681</v>
+        <v>2679</v>
       </c>
       <c r="D927" t="e">
         <f>VLOOKUP(C927,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="928" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="928" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A928" t="s">
         <v>2074</v>
       </c>
@@ -28373,9 +28369,9 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="932" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="932" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A932" t="s">
-        <v>2682</v>
+        <v>2680</v>
       </c>
       <c r="B932">
         <v>0.02</v>
@@ -28403,9 +28399,9 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="934" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="934" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A934" t="s">
-        <v>2683</v>
+        <v>2681</v>
       </c>
       <c r="B934">
         <v>0.02</v>
@@ -28435,7 +28431,7 @@
     </row>
     <row r="936" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A936" t="s">
-        <v>2684</v>
+        <v>2682</v>
       </c>
       <c r="B936">
         <v>0.01</v>
@@ -28478,7 +28474,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="939" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="939" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A939" t="s">
         <v>2339</v>
       </c>
@@ -28495,20 +28491,20 @@
     </row>
     <row r="940" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A940" t="s">
-        <v>2685</v>
+        <v>2683</v>
       </c>
       <c r="B940">
         <v>0.01</v>
       </c>
       <c r="C940" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="D940" t="e">
         <f>VLOOKUP(C940,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="941" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="941" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A941" t="s">
         <v>1585</v>
       </c>
@@ -28523,7 +28519,7 @@
         <v>US1890541097</v>
       </c>
     </row>
-    <row r="942" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="942" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A942" t="s">
         <v>1571</v>
       </c>
@@ -28553,9 +28549,9 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="944" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="944" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A944" t="s">
-        <v>2411</v>
+        <v>2409</v>
       </c>
       <c r="B944">
         <v>0.01</v>
@@ -28568,7 +28564,7 @@
         <v>JP3300200007</v>
       </c>
     </row>
-    <row r="945" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="945" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A945" t="s">
         <v>275</v>
       </c>
@@ -28585,13 +28581,13 @@
     </row>
     <row r="946" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A946" t="s">
-        <v>2687</v>
+        <v>2685</v>
       </c>
       <c r="B946">
         <v>0.01</v>
       </c>
       <c r="C946" t="s">
-        <v>2688</v>
+        <v>2686</v>
       </c>
       <c r="D946" t="e">
         <f>VLOOKUP(C946,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -28600,13 +28596,13 @@
     </row>
     <row r="947" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A947" t="s">
-        <v>2689</v>
+        <v>2687</v>
       </c>
       <c r="B947">
         <v>0.01</v>
       </c>
       <c r="C947" t="s">
-        <v>2690</v>
+        <v>2688</v>
       </c>
       <c r="D947" t="e">
         <f>VLOOKUP(C947,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -28628,7 +28624,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="949" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="949" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A949" t="s">
         <v>26</v>
       </c>
@@ -28673,7 +28669,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="952" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="952" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A952" t="s">
         <v>2022</v>
       </c>
@@ -28690,20 +28686,20 @@
     </row>
     <row r="953" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A953" t="s">
-        <v>2691</v>
+        <v>2689</v>
       </c>
       <c r="B953">
         <v>0.01</v>
       </c>
       <c r="C953" t="s">
-        <v>2692</v>
+        <v>2690</v>
       </c>
       <c r="D953" t="e">
         <f>VLOOKUP(C953,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="954" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="954" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A954" t="s">
         <v>2151</v>
       </c>
@@ -28765,20 +28761,20 @@
     </row>
     <row r="958" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A958" t="s">
-        <v>2693</v>
+        <v>2691</v>
       </c>
       <c r="B958">
         <v>0.01</v>
       </c>
       <c r="C958" t="s">
-        <v>2694</v>
+        <v>2692</v>
       </c>
       <c r="D958" t="e">
         <f>VLOOKUP(C958,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="959" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="959" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A959" t="s">
         <v>905</v>
       </c>
@@ -28793,15 +28789,15 @@
         <v>CA3759161035</v>
       </c>
     </row>
-    <row r="960" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="960" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A960" t="s">
-        <v>2695</v>
+        <v>2693</v>
       </c>
       <c r="B960">
         <v>0.01</v>
       </c>
       <c r="C960" t="s">
-        <v>2437</v>
+        <v>2435</v>
       </c>
       <c r="D960" t="str">
         <f>VLOOKUP(C960,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -28853,7 +28849,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="964" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="964" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A964" t="s">
         <v>1936</v>
       </c>
@@ -28868,7 +28864,7 @@
         <v>BE0974264930</v>
       </c>
     </row>
-    <row r="965" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="965" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A965" t="s">
         <v>2348</v>
       </c>
@@ -28883,7 +28879,7 @@
         <v>US12008R1077</v>
       </c>
     </row>
-    <row r="966" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="966" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A966" t="s">
         <v>2070</v>
       </c>
@@ -28913,7 +28909,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="968" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="968" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A968" t="s">
         <v>1980</v>
       </c>
@@ -28945,13 +28941,13 @@
     </row>
     <row r="970" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A970" t="s">
-        <v>2696</v>
+        <v>2694</v>
       </c>
       <c r="B970">
         <v>0.01</v>
       </c>
       <c r="C970" t="s">
-        <v>2697</v>
+        <v>2695</v>
       </c>
       <c r="D970" t="e">
         <f>VLOOKUP(C970,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -29033,7 +29029,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="976" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="976" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A976" t="s">
         <v>1309</v>
       </c>
@@ -29101,14 +29097,14 @@
         <v>0.01</v>
       </c>
       <c r="C980" t="s">
-        <v>2698</v>
+        <v>2696</v>
       </c>
       <c r="D980" t="e">
         <f>VLOOKUP(C980,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="981" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="981" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A981" t="s">
         <v>522</v>
       </c>
@@ -29125,13 +29121,13 @@
     </row>
     <row r="982" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A982" t="s">
-        <v>2699</v>
+        <v>2697</v>
       </c>
       <c r="B982">
         <v>0.01</v>
       </c>
       <c r="C982" t="s">
-        <v>2700</v>
+        <v>2698</v>
       </c>
       <c r="D982" t="e">
         <f>VLOOKUP(C982,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -29168,9 +29164,9 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="985" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="985" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A985" t="s">
-        <v>2701</v>
+        <v>2699</v>
       </c>
       <c r="B985">
         <v>0.01</v>
@@ -29198,7 +29194,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="987" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="987" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A987" t="s">
         <v>1022</v>
       </c>
@@ -29213,7 +29209,7 @@
         <v>JP3814800003</v>
       </c>
     </row>
-    <row r="988" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="988" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A988" t="s">
         <v>1895</v>
       </c>
@@ -29228,7 +29224,7 @@
         <v>DK0060252690</v>
       </c>
     </row>
-    <row r="989" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="989" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A989" t="s">
         <v>2133</v>
       </c>
@@ -29243,15 +29239,15 @@
         <v>SE0005190238</v>
       </c>
     </row>
-    <row r="990" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="990" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A990" t="s">
-        <v>2409</v>
+        <v>2407</v>
       </c>
       <c r="B990">
         <v>0.01</v>
       </c>
       <c r="C990" t="s">
-        <v>2408</v>
+        <v>2406</v>
       </c>
       <c r="D990" t="str">
         <f>VLOOKUP(C990,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -29260,13 +29256,13 @@
     </row>
     <row r="991" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A991" t="s">
-        <v>2702</v>
+        <v>2700</v>
       </c>
       <c r="B991">
         <v>0.01</v>
       </c>
       <c r="C991" t="s">
-        <v>2703</v>
+        <v>2701</v>
       </c>
       <c r="D991" t="e">
         <f>VLOOKUP(C991,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -29288,7 +29284,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="993" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="993" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A993" t="s">
         <v>2275</v>
       </c>
@@ -29318,7 +29314,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="995" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="995" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A995" t="s">
         <v>2376</v>
       </c>
@@ -29395,13 +29391,13 @@
     </row>
     <row r="1000" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1000" t="s">
-        <v>2704</v>
+        <v>2702</v>
       </c>
       <c r="B1000">
         <v>0.01</v>
       </c>
       <c r="C1000" t="s">
-        <v>2705</v>
+        <v>2703</v>
       </c>
       <c r="D1000" t="e">
         <f>VLOOKUP(C1000,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -29440,13 +29436,13 @@
     </row>
     <row r="1003" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1003" t="s">
-        <v>2706</v>
+        <v>2704</v>
       </c>
       <c r="B1003">
         <v>0.01</v>
       </c>
       <c r="C1003" t="s">
-        <v>2707</v>
+        <v>2705</v>
       </c>
       <c r="D1003" t="e">
         <f>VLOOKUP(C1003,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -29500,13 +29496,13 @@
     </row>
     <row r="1007" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1007" t="s">
-        <v>2708</v>
+        <v>2706</v>
       </c>
       <c r="B1007">
         <v>0.01</v>
       </c>
       <c r="C1007" t="s">
-        <v>2709</v>
+        <v>2707</v>
       </c>
       <c r="D1007" t="e">
         <f>VLOOKUP(C1007,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -29530,13 +29526,13 @@
     </row>
     <row r="1009" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1009" t="s">
-        <v>2710</v>
+        <v>2708</v>
       </c>
       <c r="B1009">
         <v>0.01</v>
       </c>
       <c r="C1009" t="s">
-        <v>2711</v>
+        <v>2709</v>
       </c>
       <c r="D1009" t="e">
         <f>VLOOKUP(C1009,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -29575,7 +29571,7 @@
     </row>
     <row r="1012" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1012" t="s">
-        <v>2712</v>
+        <v>2710</v>
       </c>
       <c r="B1012">
         <v>0.01</v>
@@ -29603,7 +29599,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="1014" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1014" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1014" t="s">
         <v>1918</v>
       </c>
@@ -29635,13 +29631,13 @@
     </row>
     <row r="1016" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1016" t="s">
-        <v>2713</v>
+        <v>2711</v>
       </c>
       <c r="B1016">
         <v>0.01</v>
       </c>
       <c r="C1016" t="s">
-        <v>2714</v>
+        <v>2712</v>
       </c>
       <c r="D1016" t="e">
         <f>VLOOKUP(C1016,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -29686,16 +29682,16 @@
         <v>0.01</v>
       </c>
       <c r="C1019" t="s">
-        <v>2715</v>
+        <v>2713</v>
       </c>
       <c r="D1019" t="e">
         <f>VLOOKUP(C1019,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="1020" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1020" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1020" t="s">
-        <v>2716</v>
+        <v>2714</v>
       </c>
       <c r="B1020">
         <v>0.01</v>
@@ -29710,7 +29706,7 @@
     </row>
     <row r="1021" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1021" t="s">
-        <v>2717</v>
+        <v>2715</v>
       </c>
       <c r="B1021">
         <v>0.01</v>
@@ -29738,7 +29734,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="1023" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1023" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1023" t="s">
         <v>2212</v>
       </c>
@@ -29753,7 +29749,7 @@
         <v>CA45075E1043</v>
       </c>
     </row>
-    <row r="1024" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1024" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1024" t="s">
         <v>386</v>
       </c>
@@ -29768,7 +29764,7 @@
         <v>FR0000130452</v>
       </c>
     </row>
-    <row r="1025" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1025" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1025" t="s">
         <v>606</v>
       </c>
@@ -29785,13 +29781,13 @@
     </row>
     <row r="1026" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1026" t="s">
-        <v>2718</v>
+        <v>2716</v>
       </c>
       <c r="B1026">
         <v>0.01</v>
       </c>
       <c r="C1026" t="s">
-        <v>2719</v>
+        <v>2717</v>
       </c>
       <c r="D1026" t="e">
         <f>VLOOKUP(C1026,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -29800,20 +29796,20 @@
     </row>
     <row r="1027" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1027" t="s">
-        <v>2720</v>
+        <v>2718</v>
       </c>
       <c r="B1027">
         <v>0.01</v>
       </c>
       <c r="C1027" t="s">
-        <v>2721</v>
+        <v>2719</v>
       </c>
       <c r="D1027" t="e">
         <f>VLOOKUP(C1027,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="1028" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1028" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1028" t="s">
         <v>2147</v>
       </c>
@@ -29828,7 +29824,7 @@
         <v>CA87262K1057</v>
       </c>
     </row>
-    <row r="1029" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1029" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1029" t="s">
         <v>1877</v>
       </c>
@@ -29873,7 +29869,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="1032" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1032" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1032" t="s">
         <v>1731</v>
       </c>
@@ -29888,7 +29884,7 @@
         <v>DE0005785802</v>
       </c>
     </row>
-    <row r="1033" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1033" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1033" t="s">
         <v>2383</v>
       </c>
@@ -29935,20 +29931,20 @@
     </row>
     <row r="1036" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1036" t="s">
-        <v>2722</v>
+        <v>2720</v>
       </c>
       <c r="B1036">
         <v>0.01</v>
       </c>
       <c r="C1036" t="s">
-        <v>2723</v>
+        <v>2721</v>
       </c>
       <c r="D1036" t="e">
         <f>VLOOKUP(C1036,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="1037" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1037" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1037" t="s">
         <v>1829</v>
       </c>
@@ -29965,13 +29961,13 @@
     </row>
     <row r="1038" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1038" t="s">
-        <v>2724</v>
+        <v>2722</v>
       </c>
       <c r="B1038">
         <v>0.01</v>
       </c>
       <c r="C1038" t="s">
-        <v>2725</v>
+        <v>2723</v>
       </c>
       <c r="D1038" t="e">
         <f>VLOOKUP(C1038,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -29980,13 +29976,13 @@
     </row>
     <row r="1039" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1039" t="s">
-        <v>2726</v>
+        <v>2724</v>
       </c>
       <c r="B1039">
         <v>0.01</v>
       </c>
       <c r="C1039" t="s">
-        <v>2727</v>
+        <v>2725</v>
       </c>
       <c r="D1039" t="e">
         <f>VLOOKUP(C1039,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -29995,7 +29991,7 @@
     </row>
     <row r="1040" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1040" t="s">
-        <v>2728</v>
+        <v>2726</v>
       </c>
       <c r="B1040">
         <v>0.01</v>
@@ -30008,7 +30004,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="1041" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1041" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1041" t="s">
         <v>1069</v>
       </c>
@@ -30025,20 +30021,20 @@
     </row>
     <row r="1042" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1042" t="s">
-        <v>2729</v>
+        <v>2727</v>
       </c>
       <c r="B1042">
         <v>0.01</v>
       </c>
       <c r="C1042" t="s">
-        <v>2730</v>
+        <v>2728</v>
       </c>
       <c r="D1042" t="e">
         <f>VLOOKUP(C1042,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="1043" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1043" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1043" t="s">
         <v>348</v>
       </c>
@@ -30055,20 +30051,20 @@
     </row>
     <row r="1044" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1044" t="s">
-        <v>2731</v>
+        <v>2729</v>
       </c>
       <c r="B1044">
         <v>0.01</v>
       </c>
       <c r="C1044" t="s">
-        <v>2732</v>
+        <v>2730</v>
       </c>
       <c r="D1044" t="e">
         <f>VLOOKUP(C1044,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="1045" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1045" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1045" t="s">
         <v>1868</v>
       </c>
@@ -30083,7 +30079,7 @@
         <v>GB00B0744B38</v>
       </c>
     </row>
-    <row r="1046" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1046" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1046" t="s">
         <v>2390</v>
       </c>
@@ -30143,7 +30139,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="1050" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1050" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1050" t="s">
         <v>1833</v>
       </c>
@@ -30173,7 +30169,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="1052" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1052" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1052" t="s">
         <v>1850</v>
       </c>
@@ -30220,13 +30216,13 @@
     </row>
     <row r="1055" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1055" t="s">
-        <v>2733</v>
+        <v>2731</v>
       </c>
       <c r="B1055">
         <v>0.01</v>
       </c>
       <c r="C1055" t="s">
-        <v>2734</v>
+        <v>2732</v>
       </c>
       <c r="D1055" t="e">
         <f>VLOOKUP(C1055,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -30278,7 +30274,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="1059" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1059" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1059" t="s">
         <v>2004</v>
       </c>
@@ -30295,13 +30291,13 @@
     </row>
     <row r="1060" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1060" t="s">
-        <v>2735</v>
+        <v>2733</v>
       </c>
       <c r="B1060">
         <v>0.01</v>
       </c>
       <c r="C1060" t="s">
-        <v>2736</v>
+        <v>2734</v>
       </c>
       <c r="D1060" t="e">
         <f>VLOOKUP(C1060,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -30325,20 +30321,20 @@
     </row>
     <row r="1062" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1062" t="s">
-        <v>2737</v>
+        <v>2735</v>
       </c>
       <c r="B1062">
         <v>0.01</v>
       </c>
       <c r="C1062" t="s">
-        <v>2738</v>
+        <v>2736</v>
       </c>
       <c r="D1062" t="e">
         <f>VLOOKUP(C1062,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="1063" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1063" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1063" t="s">
         <v>2184</v>
       </c>
@@ -30370,13 +30366,13 @@
     </row>
     <row r="1065" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1065" t="s">
-        <v>2739</v>
+        <v>2737</v>
       </c>
       <c r="B1065">
         <v>0.01</v>
       </c>
       <c r="C1065" t="s">
-        <v>2740</v>
+        <v>2738</v>
       </c>
       <c r="D1065" t="e">
         <f>VLOOKUP(C1065,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -30430,13 +30426,13 @@
     </row>
     <row r="1069" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1069" t="s">
-        <v>2741</v>
+        <v>2739</v>
       </c>
       <c r="B1069">
         <v>0.01</v>
       </c>
       <c r="C1069" t="s">
-        <v>2742</v>
+        <v>2740</v>
       </c>
       <c r="D1069" t="e">
         <f>VLOOKUP(C1069,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -30445,13 +30441,13 @@
     </row>
     <row r="1070" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1070" t="s">
-        <v>2743</v>
+        <v>2741</v>
       </c>
       <c r="B1070">
         <v>0.01</v>
       </c>
       <c r="C1070" t="s">
-        <v>2744</v>
+        <v>2742</v>
       </c>
       <c r="D1070" t="e">
         <f>VLOOKUP(C1070,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -30460,13 +30456,13 @@
     </row>
     <row r="1071" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1071" t="s">
-        <v>2745</v>
+        <v>2743</v>
       </c>
       <c r="B1071">
         <v>0.01</v>
       </c>
       <c r="C1071" t="s">
-        <v>2746</v>
+        <v>2744</v>
       </c>
       <c r="D1071" t="e">
         <f>VLOOKUP(C1071,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -30490,13 +30486,13 @@
     </row>
     <row r="1073" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1073" t="s">
-        <v>2747</v>
+        <v>2745</v>
       </c>
       <c r="B1073">
         <v>0.01</v>
       </c>
       <c r="C1073" t="s">
-        <v>2748</v>
+        <v>2746</v>
       </c>
       <c r="D1073" t="e">
         <f>VLOOKUP(C1073,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -30535,7 +30531,7 @@
     </row>
     <row r="1076" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1076" t="s">
-        <v>2749</v>
+        <v>2747</v>
       </c>
       <c r="B1076">
         <v>0.01</v>
@@ -30550,13 +30546,13 @@
     </row>
     <row r="1077" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1077" t="s">
-        <v>2750</v>
+        <v>2748</v>
       </c>
       <c r="B1077">
         <v>0.01</v>
       </c>
       <c r="C1077" t="s">
-        <v>2751</v>
+        <v>2749</v>
       </c>
       <c r="D1077" t="e">
         <f>VLOOKUP(C1077,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -30578,9 +30574,9 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="1079" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1079" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1079" t="s">
-        <v>2752</v>
+        <v>2750</v>
       </c>
       <c r="B1079">
         <v>0.01</v>
@@ -30610,7 +30606,7 @@
     </row>
     <row r="1081" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1081" t="s">
-        <v>2753</v>
+        <v>2751</v>
       </c>
       <c r="B1081">
         <v>0.01</v>
@@ -30625,13 +30621,13 @@
     </row>
     <row r="1082" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1082" t="s">
-        <v>2754</v>
+        <v>2752</v>
       </c>
       <c r="B1082">
         <v>0.01</v>
       </c>
       <c r="C1082" t="s">
-        <v>2755</v>
+        <v>2753</v>
       </c>
       <c r="D1082" t="e">
         <f>VLOOKUP(C1082,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -30640,13 +30636,13 @@
     </row>
     <row r="1083" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1083" t="s">
-        <v>2756</v>
+        <v>2754</v>
       </c>
       <c r="B1083">
         <v>0.01</v>
       </c>
       <c r="C1083" t="s">
-        <v>2757</v>
+        <v>2755</v>
       </c>
       <c r="D1083" t="e">
         <f>VLOOKUP(C1083,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -30775,7 +30771,7 @@
     </row>
     <row r="1092" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1092" t="s">
-        <v>2758</v>
+        <v>2756</v>
       </c>
       <c r="B1092">
         <v>0.01</v>
@@ -30835,20 +30831,20 @@
     </row>
     <row r="1096" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1096" t="s">
-        <v>2759</v>
+        <v>2757</v>
       </c>
       <c r="B1096">
         <v>0.01</v>
       </c>
       <c r="C1096" t="s">
-        <v>2760</v>
+        <v>2758</v>
       </c>
       <c r="D1096" t="e">
         <f>VLOOKUP(C1096,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="1097" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1097" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1097" t="s">
         <v>2055</v>
       </c>
@@ -30863,7 +30859,7 @@
         <v>SE0000113250</v>
       </c>
     </row>
-    <row r="1098" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1098" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1098" t="s">
         <v>1031</v>
       </c>
@@ -30880,7 +30876,7 @@
     </row>
     <row r="1099" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1099" t="s">
-        <v>2761</v>
+        <v>2759</v>
       </c>
       <c r="B1099">
         <v>0.01</v>
@@ -30893,7 +30889,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="1100" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1100" t="s">
         <v>2185</v>
       </c>
@@ -30908,9 +30904,9 @@
         <v>FR0000121964</v>
       </c>
     </row>
-    <row r="1101" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1101" t="s">
-        <v>2762</v>
+        <v>2760</v>
       </c>
       <c r="B1101">
         <v>0.01</v>
@@ -30953,7 +30949,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="1104" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1104" t="s">
         <v>2072</v>
       </c>
@@ -30968,7 +30964,7 @@
         <v>AU000000SGP0</v>
       </c>
     </row>
-    <row r="1105" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1105" t="s">
         <v>1122</v>
       </c>
@@ -31000,13 +30996,13 @@
     </row>
     <row r="1107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1107" t="s">
-        <v>2763</v>
+        <v>2761</v>
       </c>
       <c r="B1107">
         <v>0.01</v>
       </c>
       <c r="C1107" t="s">
-        <v>2764</v>
+        <v>2762</v>
       </c>
       <c r="D1107" t="e">
         <f>VLOOKUP(C1107,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -31015,13 +31011,13 @@
     </row>
     <row r="1108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1108" t="s">
-        <v>2765</v>
+        <v>2763</v>
       </c>
       <c r="B1108">
         <v>0.01</v>
       </c>
       <c r="C1108" t="s">
-        <v>2766</v>
+        <v>2764</v>
       </c>
       <c r="D1108" t="e">
         <f>VLOOKUP(C1108,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -31030,13 +31026,13 @@
     </row>
     <row r="1109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1109" t="s">
-        <v>2767</v>
+        <v>2765</v>
       </c>
       <c r="B1109">
         <v>0.01</v>
       </c>
       <c r="C1109" t="s">
-        <v>2768</v>
+        <v>2766</v>
       </c>
       <c r="D1109" t="e">
         <f>VLOOKUP(C1109,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -31073,7 +31069,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="1112" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1112" t="s">
         <v>2115</v>
       </c>
@@ -31090,13 +31086,13 @@
     </row>
     <row r="1113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1113" t="s">
-        <v>2769</v>
+        <v>2767</v>
       </c>
       <c r="B1113">
         <v>0.01</v>
       </c>
       <c r="C1113" t="s">
-        <v>2770</v>
+        <v>2768</v>
       </c>
       <c r="D1113" t="e">
         <f>VLOOKUP(C1113,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -31120,7 +31116,7 @@
     </row>
     <row r="1115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1115" t="s">
-        <v>2771</v>
+        <v>2769</v>
       </c>
       <c r="B1115">
         <v>0.01</v>
@@ -31133,7 +31129,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="1116" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1116" t="s">
         <v>1090</v>
       </c>
@@ -31150,13 +31146,13 @@
     </row>
     <row r="1117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1117" t="s">
-        <v>2772</v>
+        <v>2770</v>
       </c>
       <c r="B1117">
         <v>0.01</v>
       </c>
       <c r="C1117" t="s">
-        <v>2773</v>
+        <v>2771</v>
       </c>
       <c r="D1117" t="e">
         <f>VLOOKUP(C1117,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -31285,13 +31281,13 @@
     </row>
     <row r="1126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1126" t="s">
-        <v>2774</v>
+        <v>2772</v>
       </c>
       <c r="B1126">
         <v>0.01</v>
       </c>
       <c r="C1126" t="s">
-        <v>2775</v>
+        <v>2773</v>
       </c>
       <c r="D1126" t="e">
         <f>VLOOKUP(C1126,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -31343,7 +31339,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="1130" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1130" t="s">
         <v>1055</v>
       </c>
@@ -31360,7 +31356,7 @@
     </row>
     <row r="1131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1131" t="s">
-        <v>2776</v>
+        <v>2774</v>
       </c>
       <c r="B1131">
         <v>0.01</v>
@@ -31405,13 +31401,13 @@
     </row>
     <row r="1134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1134" t="s">
-        <v>2777</v>
+        <v>2775</v>
       </c>
       <c r="B1134">
         <v>0.01</v>
       </c>
       <c r="C1134" t="s">
-        <v>2778</v>
+        <v>2776</v>
       </c>
       <c r="D1134" t="e">
         <f>VLOOKUP(C1134,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -31420,13 +31416,13 @@
     </row>
     <row r="1135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1135" t="s">
-        <v>2779</v>
+        <v>2777</v>
       </c>
       <c r="B1135">
         <v>0.01</v>
       </c>
       <c r="C1135" t="s">
-        <v>2780</v>
+        <v>2778</v>
       </c>
       <c r="D1135" t="e">
         <f>VLOOKUP(C1135,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -31493,7 +31489,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="1140" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1140" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1140" t="s">
         <v>759</v>
       </c>
@@ -31540,7 +31536,7 @@
     </row>
     <row r="1143" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1143" t="s">
-        <v>2781</v>
+        <v>2779</v>
       </c>
       <c r="B1143">
         <v>0.01</v>
@@ -31613,7 +31609,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="1148" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1148" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1148" t="s">
         <v>1029</v>
       </c>
@@ -31643,22 +31639,22 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="1150" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1150" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1150" t="s">
-        <v>2782</v>
+        <v>2780</v>
       </c>
       <c r="B1150">
         <v>0.01</v>
       </c>
       <c r="C1150" t="s">
-        <v>2419</v>
+        <v>2417</v>
       </c>
       <c r="D1150" t="str">
         <f>VLOOKUP(C1150,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
         <v>JP3869010003</v>
       </c>
     </row>
-    <row r="1151" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1151" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1151" t="s">
         <v>2219</v>
       </c>
@@ -31690,13 +31686,13 @@
     </row>
     <row r="1153" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1153" t="s">
-        <v>2783</v>
+        <v>2781</v>
       </c>
       <c r="B1153">
         <v>0.01</v>
       </c>
       <c r="C1153" t="s">
-        <v>2784</v>
+        <v>2782</v>
       </c>
       <c r="D1153" t="e">
         <f>VLOOKUP(C1153,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -31705,13 +31701,13 @@
     </row>
     <row r="1154" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1154" t="s">
-        <v>2785</v>
+        <v>2783</v>
       </c>
       <c r="B1154">
         <v>0.01</v>
       </c>
       <c r="C1154" t="s">
-        <v>2786</v>
+        <v>2784</v>
       </c>
       <c r="D1154" t="e">
         <f>VLOOKUP(C1154,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -31720,7 +31716,7 @@
     </row>
     <row r="1155" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1155" t="s">
-        <v>2787</v>
+        <v>2785</v>
       </c>
       <c r="B1155">
         <v>0.01</v>
@@ -31750,20 +31746,20 @@
     </row>
     <row r="1157" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1157" t="s">
-        <v>2788</v>
+        <v>2786</v>
       </c>
       <c r="B1157">
         <v>0.01</v>
       </c>
       <c r="C1157" t="s">
-        <v>2789</v>
+        <v>2787</v>
       </c>
       <c r="D1157" t="e">
         <f>VLOOKUP(C1157,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="1158" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1158" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1158" t="s">
         <v>2114</v>
       </c>
@@ -31780,13 +31776,13 @@
     </row>
     <row r="1159" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1159" t="s">
-        <v>2790</v>
+        <v>2788</v>
       </c>
       <c r="B1159">
         <v>0.01</v>
       </c>
       <c r="C1159" t="s">
-        <v>2791</v>
+        <v>2789</v>
       </c>
       <c r="D1159" t="e">
         <f>VLOOKUP(C1159,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -31823,15 +31819,15 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="1162" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1162" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1162" t="s">
-        <v>2792</v>
+        <v>2790</v>
       </c>
       <c r="B1162">
         <v>0.01</v>
       </c>
       <c r="C1162" t="s">
-        <v>2406</v>
+        <v>2404</v>
       </c>
       <c r="D1162" t="str">
         <f>VLOOKUP(C1162,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -31885,20 +31881,20 @@
     </row>
     <row r="1166" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1166" t="s">
-        <v>2793</v>
+        <v>2791</v>
       </c>
       <c r="B1166">
         <v>0.01</v>
       </c>
       <c r="C1166" t="s">
-        <v>2794</v>
+        <v>2792</v>
       </c>
       <c r="D1166" t="e">
         <f>VLOOKUP(C1166,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="1167" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1167" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1167" t="s">
         <v>1781</v>
       </c>
@@ -31928,7 +31924,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="1169" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1169" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1169" t="s">
         <v>2238</v>
       </c>
@@ -31943,15 +31939,15 @@
         <v>FI0009014377</v>
       </c>
     </row>
-    <row r="1170" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1170" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1170" t="s">
-        <v>2795</v>
+        <v>2793</v>
       </c>
       <c r="B1170">
         <v>0.01</v>
       </c>
       <c r="C1170" t="s">
-        <v>2449</v>
+        <v>2447</v>
       </c>
       <c r="D1170" t="str">
         <f>VLOOKUP(C1170,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -31988,7 +31984,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="1173" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1173" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1173" t="s">
         <v>2196</v>
       </c>
@@ -32005,7 +32001,7 @@
     </row>
     <row r="1174" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1174" t="s">
-        <v>2796</v>
+        <v>2794</v>
       </c>
       <c r="B1174">
         <v>0.01</v>
@@ -32020,20 +32016,20 @@
     </row>
     <row r="1175" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1175" t="s">
-        <v>2797</v>
+        <v>2795</v>
       </c>
       <c r="B1175">
         <v>0.01</v>
       </c>
       <c r="C1175" t="s">
-        <v>2798</v>
+        <v>2796</v>
       </c>
       <c r="D1175" t="e">
         <f>VLOOKUP(C1175,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="1176" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1176" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1176" t="s">
         <v>2175</v>
       </c>
@@ -32080,13 +32076,13 @@
     </row>
     <row r="1179" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1179" t="s">
-        <v>2799</v>
+        <v>2797</v>
       </c>
       <c r="B1179">
         <v>0.01</v>
       </c>
       <c r="C1179" t="s">
-        <v>2800</v>
+        <v>2798</v>
       </c>
       <c r="D1179" t="e">
         <f>VLOOKUP(C1179,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -32110,20 +32106,20 @@
     </row>
     <row r="1181" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1181" t="s">
-        <v>2801</v>
+        <v>2799</v>
       </c>
       <c r="B1181">
         <v>0.01</v>
       </c>
       <c r="C1181" t="s">
-        <v>2802</v>
+        <v>2800</v>
       </c>
       <c r="D1181" t="e">
         <f>VLOOKUP(C1181,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="1182" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1182" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1182" t="s">
         <v>1915</v>
       </c>
@@ -32155,7 +32151,7 @@
     </row>
     <row r="1184" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1184" t="s">
-        <v>2803</v>
+        <v>2801</v>
       </c>
       <c r="B1184">
         <v>0.01</v>
@@ -32251,7 +32247,7 @@
         <v>0.01</v>
       </c>
       <c r="C1190" t="s">
-        <v>2804</v>
+        <v>2802</v>
       </c>
       <c r="D1190" t="e">
         <f>VLOOKUP(C1190,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -32273,7 +32269,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="1192" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1192" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1192" t="s">
         <v>2121</v>
       </c>
@@ -32333,7 +32329,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="1196" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1196" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1196" t="s">
         <v>1986</v>
       </c>
@@ -32348,7 +32344,7 @@
         <v>JP3749400002</v>
       </c>
     </row>
-    <row r="1197" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1197" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1197" t="s">
         <v>2173</v>
       </c>
@@ -32395,13 +32391,13 @@
     </row>
     <row r="1200" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1200" t="s">
-        <v>2805</v>
+        <v>2803</v>
       </c>
       <c r="B1200">
         <v>0.01</v>
       </c>
       <c r="C1200" t="s">
-        <v>2806</v>
+        <v>2804</v>
       </c>
       <c r="D1200" t="e">
         <f>VLOOKUP(C1200,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -32483,7 +32479,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="1206" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1206" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1206" t="s">
         <v>741</v>
       </c>
@@ -32513,15 +32509,15 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="1208" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1208" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1208" t="s">
-        <v>2442</v>
+        <v>2440</v>
       </c>
       <c r="B1208">
         <v>0.01</v>
       </c>
       <c r="C1208" t="s">
-        <v>2441</v>
+        <v>2439</v>
       </c>
       <c r="D1208" t="str">
         <f>VLOOKUP(C1208,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -32530,13 +32526,13 @@
     </row>
     <row r="1209" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1209" t="s">
-        <v>2807</v>
+        <v>2805</v>
       </c>
       <c r="B1209">
         <v>0.01</v>
       </c>
       <c r="C1209" t="s">
-        <v>2808</v>
+        <v>2806</v>
       </c>
       <c r="D1209" t="e">
         <f>VLOOKUP(C1209,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -32560,13 +32556,13 @@
     </row>
     <row r="1211" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1211" t="s">
-        <v>2809</v>
+        <v>2807</v>
       </c>
       <c r="B1211">
         <v>0.01</v>
       </c>
       <c r="C1211" t="s">
-        <v>2810</v>
+        <v>2808</v>
       </c>
       <c r="D1211" t="e">
         <f>VLOOKUP(C1211,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -32575,13 +32571,13 @@
     </row>
     <row r="1212" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1212" t="s">
-        <v>2811</v>
+        <v>2809</v>
       </c>
       <c r="B1212">
         <v>0.01</v>
       </c>
       <c r="C1212" t="s">
-        <v>2812</v>
+        <v>2810</v>
       </c>
       <c r="D1212" t="e">
         <f>VLOOKUP(C1212,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -32605,13 +32601,13 @@
     </row>
     <row r="1214" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1214" t="s">
-        <v>2813</v>
+        <v>2811</v>
       </c>
       <c r="B1214">
         <v>0.01</v>
       </c>
       <c r="C1214" t="s">
-        <v>2814</v>
+        <v>2812</v>
       </c>
       <c r="D1214" t="e">
         <f>VLOOKUP(C1214,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -32635,7 +32631,7 @@
     </row>
     <row r="1216" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1216" t="s">
-        <v>2815</v>
+        <v>2813</v>
       </c>
       <c r="B1216">
         <v>0.01</v>
@@ -32663,7 +32659,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="1218" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1218" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1218" t="s">
         <v>2036</v>
       </c>
@@ -32695,13 +32691,13 @@
     </row>
     <row r="1220" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1220" t="s">
-        <v>2816</v>
+        <v>2814</v>
       </c>
       <c r="B1220">
         <v>0.01</v>
       </c>
       <c r="C1220" t="s">
-        <v>2817</v>
+        <v>2815</v>
       </c>
       <c r="D1220" t="e">
         <f>VLOOKUP(C1220,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -32783,7 +32779,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="1226" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1226" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1226" t="s">
         <v>2221</v>
       </c>
@@ -32830,13 +32826,13 @@
     </row>
     <row r="1229" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1229" t="s">
-        <v>2818</v>
+        <v>2816</v>
       </c>
       <c r="B1229">
         <v>0.01</v>
       </c>
       <c r="C1229" t="s">
-        <v>2819</v>
+        <v>2817</v>
       </c>
       <c r="D1229" t="e">
         <f>VLOOKUP(C1229,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -32845,13 +32841,13 @@
     </row>
     <row r="1230" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1230" t="s">
-        <v>2820</v>
+        <v>2818</v>
       </c>
       <c r="B1230">
         <v>0.01</v>
       </c>
       <c r="C1230" t="s">
-        <v>2821</v>
+        <v>2819</v>
       </c>
       <c r="D1230" t="e">
         <f>VLOOKUP(C1230,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -32860,13 +32856,13 @@
     </row>
     <row r="1231" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1231" t="s">
-        <v>2822</v>
+        <v>2820</v>
       </c>
       <c r="B1231">
         <v>0.01</v>
       </c>
       <c r="C1231" t="s">
-        <v>2823</v>
+        <v>2821</v>
       </c>
       <c r="D1231" t="e">
         <f>VLOOKUP(C1231,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -32903,7 +32899,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="1234" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1234" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1234" t="s">
         <v>1856</v>
       </c>
@@ -32920,13 +32916,13 @@
     </row>
     <row r="1235" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1235" t="s">
-        <v>2824</v>
+        <v>2822</v>
       </c>
       <c r="B1235">
         <v>0.01</v>
       </c>
       <c r="C1235" t="s">
-        <v>2825</v>
+        <v>2823</v>
       </c>
       <c r="D1235" t="e">
         <f>VLOOKUP(C1235,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -32935,13 +32931,13 @@
     </row>
     <row r="1236" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1236" t="s">
-        <v>2826</v>
+        <v>2824</v>
       </c>
       <c r="B1236">
         <v>0.01</v>
       </c>
       <c r="C1236" t="s">
-        <v>2827</v>
+        <v>2825</v>
       </c>
       <c r="D1236" t="e">
         <f>VLOOKUP(C1236,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -32965,13 +32961,13 @@
     </row>
     <row r="1238" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1238" t="s">
-        <v>2828</v>
+        <v>2826</v>
       </c>
       <c r="B1238">
         <v>0.01</v>
       </c>
       <c r="C1238" t="s">
-        <v>2829</v>
+        <v>2827</v>
       </c>
       <c r="D1238" t="e">
         <f>VLOOKUP(C1238,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -32995,13 +32991,13 @@
     </row>
     <row r="1240" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1240" t="s">
-        <v>2830</v>
+        <v>2828</v>
       </c>
       <c r="B1240">
         <v>0.01</v>
       </c>
       <c r="C1240" t="s">
-        <v>2831</v>
+        <v>2829</v>
       </c>
       <c r="D1240" t="e">
         <f>VLOOKUP(C1240,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -33023,7 +33019,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="1242" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1242" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1242" t="s">
         <v>2263</v>
       </c>
@@ -33053,7 +33049,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="1244" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1244" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1244" t="s">
         <v>2204</v>
       </c>
@@ -33085,20 +33081,20 @@
     </row>
     <row r="1246" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1246" t="s">
-        <v>2832</v>
+        <v>2830</v>
       </c>
       <c r="B1246">
         <v>0.01</v>
       </c>
       <c r="C1246" t="s">
-        <v>2833</v>
+        <v>2831</v>
       </c>
       <c r="D1246" t="e">
         <f>VLOOKUP(C1246,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="1247" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1247" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1247" t="s">
         <v>2017</v>
       </c>
@@ -33130,20 +33126,20 @@
     </row>
     <row r="1249" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1249" t="s">
-        <v>2834</v>
+        <v>2832</v>
       </c>
       <c r="B1249">
         <v>0.01</v>
       </c>
       <c r="C1249" t="s">
-        <v>2835</v>
+        <v>2833</v>
       </c>
       <c r="D1249" t="e">
         <f>VLOOKUP(C1249,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="1250" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1250" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1250" t="s">
         <v>1975</v>
       </c>
@@ -33158,7 +33154,7 @@
         <v>JP3862400003</v>
       </c>
     </row>
-    <row r="1251" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1251" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1251" t="s">
         <v>918</v>
       </c>
@@ -33173,7 +33169,7 @@
         <v>JP3783420007</v>
       </c>
     </row>
-    <row r="1252" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1252" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1252" t="s">
         <v>1105</v>
       </c>
@@ -33188,7 +33184,7 @@
         <v>JP3955000009</v>
       </c>
     </row>
-    <row r="1253" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1253" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1253" t="s">
         <v>2186</v>
       </c>
@@ -33220,13 +33216,13 @@
     </row>
     <row r="1255" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1255" t="s">
-        <v>2836</v>
+        <v>2834</v>
       </c>
       <c r="B1255">
         <v>0.01</v>
       </c>
       <c r="C1255" t="s">
-        <v>2837</v>
+        <v>2835</v>
       </c>
       <c r="D1255" t="e">
         <f>VLOOKUP(C1255,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -33235,13 +33231,13 @@
     </row>
     <row r="1256" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1256" t="s">
-        <v>2838</v>
+        <v>2836</v>
       </c>
       <c r="B1256">
         <v>0.01</v>
       </c>
       <c r="C1256" t="s">
-        <v>2839</v>
+        <v>2837</v>
       </c>
       <c r="D1256" t="e">
         <f>VLOOKUP(C1256,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -33323,7 +33319,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="1262" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1262" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1262" t="s">
         <v>2202</v>
       </c>
@@ -33338,7 +33334,7 @@
         <v>FR0004125920</v>
       </c>
     </row>
-    <row r="1263" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1263" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1263" t="s">
         <v>2169</v>
       </c>
@@ -33413,7 +33409,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="1268" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1268" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1268" t="s">
         <v>2207</v>
       </c>
@@ -33430,13 +33426,13 @@
     </row>
     <row r="1269" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1269" t="s">
-        <v>2840</v>
+        <v>2838</v>
       </c>
       <c r="B1269">
         <v>0.01</v>
       </c>
       <c r="C1269" t="s">
-        <v>2841</v>
+        <v>2839</v>
       </c>
       <c r="D1269" t="e">
         <f>VLOOKUP(C1269,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -33475,13 +33471,13 @@
     </row>
     <row r="1272" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1272" t="s">
-        <v>2842</v>
+        <v>2840</v>
       </c>
       <c r="B1272">
         <v>0</v>
       </c>
       <c r="C1272" t="s">
-        <v>2843</v>
+        <v>2841</v>
       </c>
       <c r="D1272" t="e">
         <f>VLOOKUP(C1272,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -33490,20 +33486,20 @@
     </row>
     <row r="1273" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1273" t="s">
-        <v>2844</v>
+        <v>2842</v>
       </c>
       <c r="B1273">
         <v>0</v>
       </c>
       <c r="C1273" t="s">
-        <v>2845</v>
+        <v>2843</v>
       </c>
       <c r="D1273" t="e">
         <f>VLOOKUP(C1273,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="1274" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1274" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1274" t="s">
         <v>1194</v>
       </c>
@@ -33565,13 +33561,13 @@
     </row>
     <row r="1278" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1278" t="s">
-        <v>2846</v>
+        <v>2844</v>
       </c>
       <c r="B1278">
         <v>0</v>
       </c>
       <c r="C1278" t="s">
-        <v>2847</v>
+        <v>2845</v>
       </c>
       <c r="D1278" t="e">
         <f>VLOOKUP(C1278,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -33580,13 +33576,13 @@
     </row>
     <row r="1279" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1279" t="s">
-        <v>2848</v>
+        <v>2846</v>
       </c>
       <c r="B1279">
         <v>0</v>
       </c>
       <c r="C1279" t="s">
-        <v>2849</v>
+        <v>2847</v>
       </c>
       <c r="D1279" t="e">
         <f>VLOOKUP(C1279,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -33610,13 +33606,13 @@
     </row>
     <row r="1281" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1281" t="s">
-        <v>2850</v>
+        <v>2848</v>
       </c>
       <c r="B1281">
         <v>0</v>
       </c>
       <c r="C1281" t="s">
-        <v>2851</v>
+        <v>2849</v>
       </c>
       <c r="D1281" t="e">
         <f>VLOOKUP(C1281,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -33736,7 +33732,7 @@
         <v>0</v>
       </c>
       <c r="C1289" t="s">
-        <v>2852</v>
+        <v>2850</v>
       </c>
       <c r="D1289" t="e">
         <f>VLOOKUP(C1289,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -33775,13 +33771,13 @@
     </row>
     <row r="1292" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1292" t="s">
-        <v>2853</v>
+        <v>2851</v>
       </c>
       <c r="B1292">
         <v>0</v>
       </c>
       <c r="C1292" t="s">
-        <v>2854</v>
+        <v>2852</v>
       </c>
       <c r="D1292" t="e">
         <f>VLOOKUP(C1292,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -33805,13 +33801,13 @@
     </row>
     <row r="1294" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1294" t="s">
-        <v>2855</v>
+        <v>2853</v>
       </c>
       <c r="B1294">
         <v>0</v>
       </c>
       <c r="C1294" t="s">
-        <v>2856</v>
+        <v>2854</v>
       </c>
       <c r="D1294" t="e">
         <f>VLOOKUP(C1294,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -33856,7 +33852,7 @@
         <v>0</v>
       </c>
       <c r="C1297" t="s">
-        <v>2857</v>
+        <v>2855</v>
       </c>
       <c r="D1297" t="e">
         <f>VLOOKUP(C1297,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -33865,13 +33861,13 @@
     </row>
     <row r="1298" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1298" t="s">
-        <v>2858</v>
+        <v>2856</v>
       </c>
       <c r="B1298">
         <v>0</v>
       </c>
       <c r="C1298" t="s">
-        <v>2859</v>
+        <v>2857</v>
       </c>
       <c r="D1298" t="e">
         <f>VLOOKUP(C1298,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -33880,13 +33876,13 @@
     </row>
     <row r="1299" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1299" t="s">
-        <v>2860</v>
+        <v>2858</v>
       </c>
       <c r="B1299">
         <v>0</v>
       </c>
       <c r="C1299" t="s">
-        <v>2861</v>
+        <v>2859</v>
       </c>
       <c r="D1299" t="e">
         <f>VLOOKUP(C1299,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -33908,15 +33904,15 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="1301" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1301" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1301" t="s">
-        <v>2862</v>
+        <v>2860</v>
       </c>
       <c r="B1301">
         <v>0</v>
       </c>
       <c r="C1301" t="s">
-        <v>2435</v>
+        <v>2433</v>
       </c>
       <c r="D1301" t="str">
         <f>VLOOKUP(C1301,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -33925,13 +33921,13 @@
     </row>
     <row r="1302" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1302" t="s">
-        <v>2863</v>
+        <v>2861</v>
       </c>
       <c r="B1302">
         <v>0</v>
       </c>
       <c r="C1302" t="s">
-        <v>2864</v>
+        <v>2862</v>
       </c>
       <c r="D1302" t="e">
         <f>VLOOKUP(C1302,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -33940,7 +33936,7 @@
     </row>
     <row r="1303" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1303" t="s">
-        <v>2865</v>
+        <v>2863</v>
       </c>
       <c r="B1303">
         <v>0</v>
@@ -33968,7 +33964,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="1305" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1305" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1305" t="s">
         <v>2272</v>
       </c>
@@ -34013,7 +34009,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="1308" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1308" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1308" t="s">
         <v>2271</v>
       </c>
@@ -34028,7 +34024,7 @@
         <v>JP3689500001</v>
       </c>
     </row>
-    <row r="1309" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1309" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1309" t="s">
         <v>2262</v>
       </c>
@@ -34058,7 +34054,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="1311" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1311" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1311" t="s">
         <v>2024</v>
       </c>
@@ -34105,7 +34101,7 @@
     </row>
     <row r="1314" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1314" t="s">
-        <v>2866</v>
+        <v>2864</v>
       </c>
       <c r="B1314">
         <v>0</v>
@@ -34150,13 +34146,13 @@
     </row>
     <row r="1317" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1317" t="s">
-        <v>2867</v>
+        <v>2865</v>
       </c>
       <c r="B1317">
         <v>0</v>
       </c>
       <c r="C1317" t="s">
-        <v>2868</v>
+        <v>2866</v>
       </c>
       <c r="D1317" t="e">
         <f>VLOOKUP(C1317,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -34165,20 +34161,20 @@
     </row>
     <row r="1318" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1318" t="s">
-        <v>2869</v>
+        <v>2867</v>
       </c>
       <c r="B1318">
         <v>0</v>
       </c>
       <c r="C1318" t="s">
-        <v>2870</v>
+        <v>2868</v>
       </c>
       <c r="D1318" t="e">
         <f>VLOOKUP(C1318,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="1319" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1319" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1319" t="s">
         <v>2286</v>
       </c>
@@ -34193,15 +34189,15 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="1320" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1320" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1320" t="s">
-        <v>2871</v>
+        <v>2869</v>
       </c>
       <c r="B1320">
         <v>0</v>
       </c>
       <c r="C1320" t="s">
-        <v>2397</v>
+        <v>2395</v>
       </c>
       <c r="D1320" t="str">
         <f>VLOOKUP(C1320,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -34225,20 +34221,20 @@
     </row>
     <row r="1322" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1322" t="s">
-        <v>2872</v>
+        <v>2870</v>
       </c>
       <c r="B1322">
         <v>0</v>
       </c>
       <c r="C1322" t="s">
-        <v>2873</v>
+        <v>2871</v>
       </c>
       <c r="D1322" t="e">
         <f>VLOOKUP(C1322,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="1323" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1323" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1323" t="s">
         <v>2201</v>
       </c>
@@ -34261,7 +34257,7 @@
         <v>0</v>
       </c>
       <c r="C1324" t="s">
-        <v>2874</v>
+        <v>2872</v>
       </c>
       <c r="D1324" t="e">
         <f>VLOOKUP(C1324,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -34270,7 +34266,7 @@
     </row>
     <row r="1325" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1325" t="s">
-        <v>2875</v>
+        <v>2873</v>
       </c>
       <c r="B1325">
         <v>0</v>
@@ -34283,7 +34279,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="1326" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1326" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1326" t="s">
         <v>2255</v>
       </c>
@@ -34328,7 +34324,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="1329" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1329" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1329" t="s">
         <v>2282</v>
       </c>
@@ -34343,7 +34339,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="1330" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1330" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1330" t="s">
         <v>2287</v>
       </c>
@@ -34358,7 +34354,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="1331" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1331" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1331" t="s">
         <v>2283</v>
       </c>
@@ -34390,13 +34386,13 @@
     </row>
     <row r="1333" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1333" t="s">
-        <v>2876</v>
+        <v>2874</v>
       </c>
       <c r="B1333">
         <v>0</v>
       </c>
       <c r="C1333" t="s">
-        <v>2877</v>
+        <v>2875</v>
       </c>
       <c r="D1333" t="e">
         <f>VLOOKUP(C1333,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -34411,7 +34407,7 @@
         <v>0</v>
       </c>
       <c r="C1334" t="s">
-        <v>2878</v>
+        <v>2876</v>
       </c>
       <c r="D1334" t="e">
         <f>VLOOKUP(C1334,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
@@ -34420,22 +34416,22 @@
     </row>
     <row r="1335" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1335" t="s">
-        <v>2879</v>
+        <v>2877</v>
       </c>
       <c r="B1335">
         <v>0</v>
       </c>
       <c r="C1335" t="s">
-        <v>2880</v>
+        <v>2878</v>
       </c>
       <c r="D1335" t="e">
         <f>VLOOKUP(C1335,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="1336" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1336" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1336" t="s">
-        <v>2881</v>
+        <v>2879</v>
       </c>
       <c r="B1336">
         <v>0</v>
@@ -34450,22 +34446,22 @@
     </row>
     <row r="1337" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1337" t="s">
-        <v>2882</v>
+        <v>2880</v>
       </c>
       <c r="B1337">
         <v>0</v>
       </c>
       <c r="C1337" t="s">
-        <v>2883</v>
+        <v>2881</v>
       </c>
       <c r="D1337" t="e">
         <f>VLOOKUP(C1337,'Achmea halfjaarverslag 2025'!A:A,1,FALSE)</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="1338" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1338" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1338" t="s">
-        <v>2884</v>
+        <v>2882</v>
       </c>
       <c r="B1338">
         <v>0</v>
@@ -34478,9 +34474,9 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="1339" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1339" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1339" t="s">
-        <v>2885</v>
+        <v>2883</v>
       </c>
       <c r="B1339">
         <v>0</v>
@@ -34493,9 +34489,9 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="1340" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1340" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1340" t="s">
-        <v>2886</v>
+        <v>2884</v>
       </c>
       <c r="B1340">
         <v>0</v>
@@ -34508,9 +34504,9 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="1341" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1341" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1341" t="s">
-        <v>2887</v>
+        <v>2885</v>
       </c>
       <c r="B1341">
         <v>0</v>
@@ -36282,861 +36278,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D1634" xr:uid="{3DC52ED4-B602-4882-BC7B-91894D5F69EC}">
-    <filterColumn colId="2">
-      <filters blank="1">
-        <filter val="AT0000606306"/>
-        <filter val="AU000000ALL7"/>
-        <filter val="AU000000ANZ3"/>
-        <filter val="AU000000APA1"/>
-        <filter val="AU000000ASX7"/>
-        <filter val="AU000000BHP4"/>
-        <filter val="AU000000CAR3"/>
-        <filter val="AU000000COH5"/>
-        <filter val="AU000000CSL8"/>
-        <filter val="AU000000EVN4"/>
-        <filter val="AU000000GMG2"/>
-        <filter val="AU000000LYC6"/>
-        <filter val="AU000000MPL3"/>
-        <filter val="AU000000MQG1"/>
-        <filter val="AU000000ORG5"/>
-        <filter val="AU000000PME8"/>
-        <filter val="AU000000QBE9"/>
-        <filter val="AU000000S320"/>
-        <filter val="AU000000SHL7"/>
-        <filter val="AU000000SIG5"/>
-        <filter val="AU000000SOL3"/>
-        <filter val="AU000000STO6"/>
-        <filter val="AU000000TCL6"/>
-        <filter val="AU000000TLS2"/>
-        <filter val="AU000000WOW2"/>
-        <filter val="AU000000WTC3"/>
-        <filter val="AU0000219529"/>
-        <filter val="AU0000224040"/>
-        <filter val="AU0000364754"/>
-        <filter val="BE0003604155"/>
-        <filter val="BE0003717312"/>
-        <filter val="BE0003739530"/>
-        <filter val="BE0003797140"/>
-        <filter val="BE0003822393"/>
-        <filter val="BE0003823409"/>
-        <filter val="BE0974259880"/>
-        <filter val="BE0974293251"/>
-        <filter val="BE0974464977"/>
-        <filter val="BMG0112X1056"/>
-        <filter val="BMG0450A1053"/>
-        <filter val="BMG2178K1009"/>
-        <filter val="BMG3223R1088"/>
-        <filter val="BMG4587L1090"/>
-        <filter val="BMG507361001"/>
-        <filter val="CA00208D4084"/>
-        <filter val="CA0115321089"/>
-        <filter val="CA01626P1484"/>
-        <filter val="CA04764T1049"/>
-        <filter val="CA05534B7604"/>
-        <filter val="CA0636711016"/>
-        <filter val="CA0641491075"/>
-        <filter val="CA0977518616"/>
-        <filter val="CA11271J1075"/>
-        <filter val="CA11285B1085"/>
-        <filter val="CA1130041058"/>
-        <filter val="CA1247651088"/>
-        <filter val="CA1249003098"/>
-        <filter val="CA12532H1047"/>
-        <filter val="CA13321L1085"/>
-        <filter val="CA1363751027"/>
-        <filter val="CA1363851017"/>
-        <filter val="CA13646K1084"/>
-        <filter val="CA1367178326"/>
-        <filter val="CA15135U1093"/>
-        <filter val="CA21037X1006"/>
-        <filter val="CA21037X1345"/>
-        <filter val="CA2499061083"/>
-        <filter val="CA2861812014"/>
-        <filter val="CA2908761018"/>
-        <filter val="CA29250N1050"/>
-        <filter val="CA3039011026"/>
-        <filter val="CA3359341052"/>
-        <filter val="CA33767E2024"/>
-        <filter val="CA3495531079"/>
-        <filter val="CA3518581051"/>
-        <filter val="CA36168Q1046"/>
-        <filter val="CA39138C1068"/>
-        <filter val="CA4488112083"/>
-        <filter val="CA4530384086"/>
-        <filter val="CA45823T1066"/>
-        <filter val="CA46579R1047"/>
-        <filter val="CA5503711080"/>
-        <filter val="CA5592224011"/>
-        <filter val="CA6330671034"/>
-        <filter val="CA67077M1086"/>
-        <filter val="CA6837151068"/>
-        <filter val="CA76131D1033"/>
-        <filter val="CA7751092007"/>
-        <filter val="CA8029121057"/>
-        <filter val="CA85472N1096"/>
-        <filter val="CA8667961053"/>
-        <filter val="CA8672241079"/>
-        <filter val="CA87241L1094"/>
-        <filter val="CA8787422044"/>
-        <filter val="CA87971M1032"/>
-        <filter val="CA8849038085"/>
-        <filter val="CA8911021050"/>
-        <filter val="CA89156V1067"/>
-        <filter val="CA92938W2022"/>
-        <filter val="CA94106B1013"/>
-        <filter val="CA9628791027"/>
-        <filter val="CA96467A2002"/>
-        <filter val="CH0008038389"/>
-        <filter val="CH0008742519"/>
-        <filter val="CH0009002962"/>
-        <filter val="CH0010570759"/>
-        <filter val="CH0010570767"/>
-        <filter val="CH0012214059"/>
-        <filter val="CH0012255151"/>
-        <filter val="CH0013841017"/>
-        <filter val="CH0016440353"/>
-        <filter val="CH0024608827"/>
-        <filter val="CH0024638212"/>
-        <filter val="CH0025238863"/>
-        <filter val="CH0025751329"/>
-        <filter val="CH0030170408"/>
-        <filter val="CH0044328745"/>
-        <filter val="CH0102484968"/>
-        <filter val="CH0126881561"/>
-        <filter val="CH0130293662"/>
-        <filter val="CH0244767585"/>
-        <filter val="CH0311864901"/>
-        <filter val="CH0418792922"/>
-        <filter val="CH0432492467"/>
-        <filter val="CH0466642201"/>
-        <filter val="CH0531751755"/>
-        <filter val="CH1101098163"/>
-        <filter val="CH1175448666"/>
-        <filter val="CH1216478797"/>
-        <filter val="CH1243598427"/>
-        <filter val="CH1256740924"/>
-        <filter val="CH1300646267"/>
-        <filter val="CH1335392721"/>
-        <filter val="CH1430134226"/>
-        <filter val="DE0005190003"/>
-        <filter val="DE0005190037"/>
-        <filter val="DE0005200000"/>
-        <filter val="DE0005439004"/>
-        <filter val="DE0005470306"/>
-        <filter val="DE0006048408"/>
-        <filter val="DE0006070006"/>
-        <filter val="DE0006231004"/>
-        <filter val="DE0006452907"/>
-        <filter val="DE0006599905"/>
-        <filter val="DE0007010803"/>
-        <filter val="DE0007030009"/>
-        <filter val="DE0007037129"/>
-        <filter val="DE0007165631"/>
-        <filter val="DE0007664039"/>
-        <filter val="DE0008232125"/>
-        <filter val="DE0008402215"/>
-        <filter val="DE000A0D9PT0"/>
-        <filter val="DE000A12DM80"/>
-        <filter val="DE000A1DAHH0"/>
-        <filter val="DE000A1EWWW0"/>
-        <filter val="DE000A1ML7J1"/>
-        <filter val="DE000A2E4K43"/>
-        <filter val="DE000BAY0017"/>
-        <filter val="DE000C7PXYX3"/>
-        <filter val="DE000CBK1001"/>
-        <filter val="DE000DTR0CK8"/>
-        <filter val="DE000HAG0005"/>
-        <filter val="DE000KBX1006"/>
-        <filter val="DE000LEG1110"/>
-        <filter val="DE000PAG9113"/>
-        <filter val="DE000PAH0038"/>
-        <filter val="DE000SHL1006"/>
-        <filter val="DE000SYM9999"/>
-        <filter val="DE000TLX1005"/>
-        <filter val="DK0010181759"/>
-        <filter val="DK0010244425"/>
-        <filter val="DK0010272202"/>
-        <filter val="DK0010274414"/>
-        <filter val="DK0060079531"/>
-        <filter val="DK0060094928"/>
-        <filter val="DK0060336014"/>
-        <filter val="DK0060448595"/>
-        <filter val="DK0060636678"/>
-        <filter val="DK0060738599"/>
-        <filter val="DK0061539921"/>
-        <filter val="ES0105066007"/>
-        <filter val="ES0109067019"/>
-        <filter val="ES0113679I37"/>
-        <filter val="ES0113860A34"/>
-        <filter val="ES0113900J37"/>
-        <filter val="ES0116870314"/>
-        <filter val="ES0124244E34"/>
-        <filter val="ES0125220311"/>
-        <filter val="ES0127797019"/>
-        <filter val="ES0167050915"/>
-        <filter val="ES0171996087"/>
-        <filter val="ES0173093024"/>
-        <filter val="ES0173516115"/>
-        <filter val="ES0177542018"/>
-        <filter val="ES0178430E18"/>
-        <filter val="FI0009000202"/>
-        <filter val="FI0009003727"/>
-        <filter val="FI0009005961"/>
-        <filter val="FI0009005987"/>
-        <filter val="FI0009007884"/>
-        <filter val="FI0009013296"/>
-        <filter val="FI0009014575"/>
-        <filter val="FI4000552500"/>
-        <filter val="FR0000039299"/>
-        <filter val="FR0000064578"/>
-        <filter val="FR0000073272"/>
-        <filter val="FR0000120073"/>
-        <filter val="FR0000120172"/>
-        <filter val="FR0000120271"/>
-        <filter val="FR0000120321"/>
-        <filter val="FR0000120404"/>
-        <filter val="FR0000120503"/>
-        <filter val="FR0000120693"/>
-        <filter val="FR0000121220"/>
-        <filter val="FR0000121329"/>
-        <filter val="FR0000121485"/>
-        <filter val="FR0000121972"/>
-        <filter val="FR0000124141"/>
-        <filter val="FR0000125338"/>
-        <filter val="FR0000125486"/>
-        <filter val="FR0000130577"/>
-        <filter val="FR0000130809"/>
-        <filter val="FR0006174348"/>
-        <filter val="FR0010040865"/>
-        <filter val="FR0010220475"/>
-        <filter val="FR0010259150"/>
-        <filter val="FR0010340141"/>
-        <filter val="FR0010451203"/>
-        <filter val="FR0010533075"/>
-        <filter val="FR0010908533"/>
-        <filter val="FR0013154002"/>
-        <filter val="FR0013326246"/>
-        <filter val="FR0013451333"/>
-        <filter val="FR0014000MR3"/>
-        <filter val="FR0014003TT8"/>
-        <filter val="FR0014004L86"/>
-        <filter val="GB0000456144"/>
-        <filter val="GB0000536739"/>
-        <filter val="GB0000811801"/>
-        <filter val="GB0002374006"/>
-        <filter val="GB0002634946"/>
-        <filter val="GB0002875804"/>
-        <filter val="GB0004052071"/>
-        <filter val="GB0004544929"/>
-        <filter val="GB0005603997"/>
-        <filter val="GB0006731235"/>
-        <filter val="GB0007099541"/>
-        <filter val="GB0007908733"/>
-        <filter val="GB0007980591"/>
-        <filter val="GB0009223206"/>
-        <filter val="GB0031638363"/>
-        <filter val="GB00B02J6398"/>
-        <filter val="GB00B082RF11"/>
-        <filter val="GB00B0LCW083"/>
-        <filter val="GB00B0SWJX34"/>
-        <filter val="GB00B19NLV48"/>
-        <filter val="GB00B1FH8J72"/>
-        <filter val="GB00B1KJJ408"/>
-        <filter val="GB00B1WY2338"/>
-        <filter val="GB00B24CGK77"/>
-        <filter val="GB00B2QPKJ12"/>
-        <filter val="GB00B39J2M42"/>
-        <filter val="GB00B5ZN1N88"/>
-        <filter val="GB00B63H8491"/>
-        <filter val="GB00B8C3BL03"/>
-        <filter val="GB00BDR05C01"/>
-        <filter val="GB00BGXQNP29"/>
-        <filter val="GB00BH4HKS39"/>
-        <filter val="GB00BKFB1C65"/>
-        <filter val="GB00BL6K5J42"/>
-        <filter val="GB00BL9YR756"/>
-        <filter val="GB00BM8Q5M07"/>
-        <filter val="GB00BMJ6DW54"/>
-        <filter val="GB00BMVP7Y09"/>
-        <filter val="GB00BMX86B70"/>
-        <filter val="GB00BN7SWP63"/>
-        <filter val="GB00BNGDN821"/>
-        <filter val="GB00BP9LHF23"/>
-        <filter val="GB00BPQY8M80"/>
-        <filter val="GB00BVZK7T90"/>
-        <filter val="GB00BWFGQN14"/>
-        <filter val="GB00BYW0PQ60"/>
-        <filter val="GB00MP9C6L33"/>
-        <filter val="HK0002007356"/>
-        <filter val="HK0003000038"/>
-        <filter val="HK0004000045"/>
-        <filter val="HK0006000050"/>
-        <filter val="HK0011000095"/>
-        <filter val="HK0016000132"/>
-        <filter val="HK0027032686"/>
-        <filter val="HK0066009694"/>
-        <filter val="HK0083000502"/>
-        <filter val="HK0823032773"/>
-        <filter val="HK2388011192"/>
-        <filter val="IE00028FXN24"/>
-        <filter val="IE0004906560"/>
-        <filter val="IE0004927939"/>
-        <filter val="IE00B50QMP13"/>
-        <filter val="IE00B8KQN827"/>
-        <filter val="IE00BDB6Q211"/>
-        <filter val="IE00BFY8C754"/>
-        <filter val="IE00BLP1HW54"/>
-        <filter val="IE00BWT6H894"/>
-        <filter val="IE00BY7QL619"/>
-        <filter val="IE00BYTBXV33"/>
-        <filter val="IL0002730112"/>
-        <filter val="IL0002810146"/>
-        <filter val="IL0006912120"/>
-        <filter val="IL0006954379"/>
-        <filter val="IL0007670123"/>
-        <filter val="IL0010811243"/>
-        <filter val="IL0010845571"/>
-        <filter val="IL0011194789"/>
-        <filter val="IL0011301780"/>
-        <filter val="IL0011334468"/>
-        <filter val="IL0011762130"/>
-        <filter val="IM00B5VQMV65"/>
-        <filter val="IT0000062072"/>
-        <filter val="IT0000066123"/>
-        <filter val="IT0000072170"/>
-        <filter val="IT0001347308"/>
-        <filter val="IT0003132476"/>
-        <filter val="IT0003153415"/>
-        <filter val="IT0003242622"/>
-        <filter val="IT0003497168"/>
-        <filter val="IT0003828271"/>
-        <filter val="IT0003856405"/>
-        <filter val="IT0004176001"/>
-        <filter val="IT0004776628"/>
-        <filter val="IT0004810054"/>
-        <filter val="IT0004965148"/>
-        <filter val="IT0005090300"/>
-        <filter val="IT0005218380"/>
-        <filter val="IT0005366767"/>
-        <filter val="IT0005508921"/>
-        <filter val="JE00B4T3BW64"/>
-        <filter val="JE00BJ1F3079"/>
-        <filter val="JE00BRX98089"/>
-        <filter val="JP3027670003"/>
-        <filter val="JP3102000001"/>
-        <filter val="JP3104890003"/>
-        <filter val="JP3111200006"/>
-        <filter val="JP3112000009"/>
-        <filter val="JP3116000005"/>
-        <filter val="JP3119600009"/>
-        <filter val="JP3134800006"/>
-        <filter val="JP3137200006"/>
-        <filter val="JP3142500002"/>
-        <filter val="JP3143600009"/>
-        <filter val="JP3160400002"/>
-        <filter val="JP3162600005"/>
-        <filter val="JP3162770006"/>
-        <filter val="JP3164720009"/>
-        <filter val="JP3166000004"/>
-        <filter val="JP3173400007"/>
-        <filter val="JP3180400008"/>
-        <filter val="JP3183200009"/>
-        <filter val="JP3188200004"/>
-        <filter val="JP3198900007"/>
-        <filter val="JP3200450009"/>
-        <filter val="JP3201200007"/>
-        <filter val="JP3205800000"/>
-        <filter val="JP3210200006"/>
-        <filter val="JP3218900003"/>
-        <filter val="JP3223800008"/>
-        <filter val="JP3224200000"/>
-        <filter val="JP3228600007"/>
-        <filter val="JP3233250004"/>
-        <filter val="JP3236200006"/>
-        <filter val="JP3236330001"/>
-        <filter val="JP3240400006"/>
-        <filter val="JP3249600002"/>
-        <filter val="JP3256000005"/>
-        <filter val="JP3258000003"/>
-        <filter val="JP3266400005"/>
-        <filter val="JP3291200008"/>
-        <filter val="JP3294460005"/>
-        <filter val="JP3304200003"/>
-        <filter val="JP3305990008"/>
-        <filter val="JP3336560002"/>
-        <filter val="JP3343200006"/>
-        <filter val="JP3351100007"/>
-        <filter val="JP3351600006"/>
-        <filter val="JP3357200009"/>
-        <filter val="JP3358000002"/>
-        <filter val="JP3360800001"/>
-        <filter val="JP3362700001"/>
-        <filter val="JP3371200001"/>
-        <filter val="JP3381000003"/>
-        <filter val="JP3386030005"/>
-        <filter val="JP3388200002"/>
-        <filter val="JP3399310006"/>
-        <filter val="JP3402600005"/>
-        <filter val="JP3404600003"/>
-        <filter val="JP3407400005"/>
-        <filter val="JP3409000001"/>
-        <filter val="JP3419400001"/>
-        <filter val="JP3420600003"/>
-        <filter val="JP3421800008"/>
-        <filter val="JP3422950000"/>
-        <filter val="JP3429300001"/>
-        <filter val="JP3429800000"/>
-        <filter val="JP3435350008"/>
-        <filter val="JP3435750009"/>
-        <filter val="JP3436100006"/>
-        <filter val="JP3436120004"/>
-        <filter val="JP3443600006"/>
-        <filter val="JP3463000004"/>
-        <filter val="JP3475350009"/>
-        <filter val="JP3476480003"/>
-        <filter val="JP3481800005"/>
-        <filter val="JP3493800001"/>
-        <filter val="JP3494600004"/>
-        <filter val="JP3496400007"/>
-        <filter val="JP3499800005"/>
-        <filter val="JP3500610005"/>
-        <filter val="JP3502200003"/>
-        <filter val="JP3511800009"/>
-        <filter val="JP3526600006"/>
-        <filter val="JP3539220008"/>
-        <filter val="JP3546800008"/>
-        <filter val="JP3548600000"/>
-        <filter val="JP3551500006"/>
-        <filter val="JP3566800003"/>
-        <filter val="JP3574200006"/>
-        <filter val="JP3583900000"/>
-        <filter val="JP3598600009"/>
-        <filter val="JP3621000003"/>
-        <filter val="JP3629000005"/>
-        <filter val="JP3634600005"/>
-        <filter val="JP3637300009"/>
-        <filter val="JP3659000008"/>
-        <filter val="JP3672400003"/>
-        <filter val="JP3705200008"/>
-        <filter val="JP3711600001"/>
-        <filter val="JP3726800000"/>
-        <filter val="JP3732000009"/>
-        <filter val="JP3734800000"/>
-        <filter val="JP3735400008"/>
-        <filter val="JP3752900005"/>
-        <filter val="JP3756100008"/>
-        <filter val="JP3756600007"/>
-        <filter val="JP3758190007"/>
-        <filter val="JP3762800005"/>
-        <filter val="JP3774200004"/>
-        <filter val="JP3778630008"/>
-        <filter val="JP3783600004"/>
-        <filter val="JP3802300008"/>
-        <filter val="JP3802400006"/>
-        <filter val="JP3814000000"/>
-        <filter val="JP3818000006"/>
-        <filter val="JP3820000002"/>
-        <filter val="JP3830800003"/>
-        <filter val="JP3854600008"/>
-        <filter val="JP3877600001"/>
-        <filter val="JP3885780001"/>
-        <filter val="JP3890310000"/>
-        <filter val="JP3892100003"/>
-        <filter val="JP3893200000"/>
-        <filter val="JP3893600001"/>
-        <filter val="JP3897700005"/>
-        <filter val="JP3898400001"/>
-        <filter val="JP3899600005"/>
-        <filter val="JP3906000009"/>
-        <filter val="JP3910660004"/>
-        <filter val="JP3914400001"/>
-        <filter val="JP3922950005"/>
-        <filter val="JP3933800009"/>
-        <filter val="JP3942400007"/>
-        <filter val="JP3942800008"/>
-        <filter val="JP3946750001"/>
-        <filter val="JP3951600000"/>
-        <filter val="JP3967200001"/>
-        <filter val="JP3976300008"/>
-        <filter val="JP3979200007"/>
-        <filter val="KYG217651051"/>
-        <filter val="KYG2177B1014"/>
-        <filter val="KYG254571055"/>
-        <filter val="KYG4124C1096"/>
-        <filter val="KYG9593A1040"/>
-        <filter val="LU1598757687"/>
-        <filter val="LU1778762911"/>
-        <filter val="LU2290522684"/>
-        <filter val="NL0000008977"/>
-        <filter val="NL0000009165"/>
-        <filter val="NL0000226223"/>
-        <filter val="NL0000235190"/>
-        <filter val="NL0000334118"/>
-        <filter val="NL0000379121"/>
-        <filter val="NL0000395903"/>
-        <filter val="NL0000687663"/>
-        <filter val="NL0009434992"/>
-        <filter val="NL0009538784"/>
-        <filter val="NL0009805522"/>
-        <filter val="NL0010545661"/>
-        <filter val="NL0010801007"/>
-        <filter val="NL0010832176"/>
-        <filter val="NL0011585146"/>
-        <filter val="NL0012059018"/>
-        <filter val="NL0012866412"/>
-        <filter val="NL0012969182"/>
-        <filter val="NL0013267909"/>
-        <filter val="NL0013654783"/>
-        <filter val="NL0014332678"/>
-        <filter val="NL00150001Q9"/>
-        <filter val="NL0015000IY2"/>
-        <filter val="NL0015001FS8"/>
-        <filter val="NL0015002CX3"/>
-        <filter val="NL0015002MS2"/>
-        <filter val="NL0015435975"/>
-        <filter val="NO0003054108"/>
-        <filter val="NO0005052605"/>
-        <filter val="NO0010096985"/>
-        <filter val="NO0010208051"/>
-        <filter val="NO0010310956"/>
-        <filter val="NO0010582521"/>
-        <filter val="NO0013536151"/>
-        <filter val="NZAIAE0002S6"/>
-        <filter val="NZCENE0001S6"/>
-        <filter val="NZIFTE0003S3"/>
-        <filter val="NZMELE0002S7"/>
-        <filter val="NZXROE0001S2"/>
-        <filter val="PTBCP0AM0015"/>
-        <filter val="PTEDP0AM0009"/>
-        <filter val="PTGAL0AM0009"/>
-        <filter val="PTJMT0AE0001"/>
-        <filter val="SE0000106270"/>
-        <filter val="SE0000107203"/>
-        <filter val="SE0000108227"/>
-        <filter val="SE0000108847"/>
-        <filter val="SE0000112724"/>
-        <filter val="SE0000114837"/>
-        <filter val="SE0000190126"/>
-        <filter val="SE0000667891"/>
-        <filter val="SE0000695876"/>
-        <filter val="SE0000872095"/>
-        <filter val="SE0005127818"/>
-        <filter val="SE0007100581"/>
-        <filter val="SE0010100958"/>
-        <filter val="SE0011090018"/>
-        <filter val="SE0012673267"/>
-        <filter val="SE0012853455"/>
-        <filter val="SE0014781795"/>
-        <filter val="SE0015658109"/>
-        <filter val="SE0015658117"/>
-        <filter val="SE0015811963"/>
-        <filter val="SE0015949201"/>
-        <filter val="SE0015949748"/>
-        <filter val="SE0015961909"/>
-        <filter val="SE0015988019"/>
-        <filter val="SE0017486889"/>
-        <filter val="SE0017486897"/>
-        <filter val="SE0017832488"/>
-        <filter val="SE0020050417"/>
-        <filter val="SE0021921269"/>
-        <filter val="SG1J26887955"/>
-        <filter val="SG1M31001969"/>
-        <filter val="SG1M51904654"/>
-        <filter val="SG1M77906915"/>
-        <filter val="SG1R50925390"/>
-        <filter val="SG1T56930848"/>
-        <filter val="SG1U68934629"/>
-        <filter val="SG9999000020"/>
-        <filter val="SGXE62145532"/>
-        <filter val="US00766T1007"/>
-        <filter val="US00827B1061"/>
-        <filter val="US00846U1016"/>
-        <filter val="US0091581068"/>
-        <filter val="US0152711091"/>
-        <filter val="US0188021085"/>
-        <filter val="US0200021014"/>
-        <filter val="US02043Q1076"/>
-        <filter val="US02156V1098"/>
-        <filter val="US02209S1033"/>
-        <filter val="US0236081024"/>
-        <filter val="US0255371017"/>
-        <filter val="US0259321042"/>
-        <filter val="US02665T3068"/>
-        <filter val="US03027X1000"/>
-        <filter val="US0304201033"/>
-        <filter val="US0311001004"/>
-        <filter val="US0311621009"/>
-        <filter val="US0326541051"/>
-        <filter val="US0367521038"/>
-        <filter val="US03769M1062"/>
-        <filter val="US0394831020"/>
-        <filter val="US03990B1017"/>
-        <filter val="US04626A1034"/>
-        <filter val="US0495601058"/>
-        <filter val="US0533321024"/>
-        <filter val="US0536111091"/>
-        <filter val="US05464C1018"/>
-        <filter val="US0584981064"/>
-        <filter val="US0718131099"/>
-        <filter val="US0758871091"/>
-        <filter val="US08265T2087"/>
-        <filter val="US0844231029"/>
-        <filter val="US0846707026"/>
-        <filter val="US09062X1037"/>
-        <filter val="US09260D1072"/>
-        <filter val="US0937121079"/>
-        <filter val="US0970231058"/>
-        <filter val="US0995021062"/>
-        <filter val="US11133T1034"/>
-        <filter val="US1152361010"/>
-        <filter val="US1156372096"/>
-        <filter val="US1220171060"/>
-        <filter val="US12503M1080"/>
-        <filter val="US12514G1085"/>
-        <filter val="US12541W2098"/>
-        <filter val="US1258961002"/>
-        <filter val="US1264081035"/>
-        <filter val="US1270971039"/>
-        <filter val="US1273871087"/>
-        <filter val="US14040H1059"/>
-        <filter val="US14316J1088"/>
-        <filter val="US14448C1045"/>
-        <filter val="US15135B1017"/>
-        <filter val="US15189T1079"/>
-        <filter val="US16119P1084"/>
-        <filter val="US1651677353"/>
-        <filter val="US1667641005"/>
-        <filter val="US1696561059"/>
-        <filter val="US1713401024"/>
-        <filter val="US1717793095"/>
-        <filter val="US1720621010"/>
-        <filter val="US18915M1071"/>
-        <filter val="US1941621039"/>
-        <filter val="US1999081045"/>
-        <filter val="US20825C1045"/>
-        <filter val="US21036P1084"/>
-        <filter val="US21037T1097"/>
-        <filter val="US2166485019"/>
-        <filter val="US2172041061"/>
-        <filter val="US21873S1087"/>
-        <filter val="US2193501051"/>
-        <filter val="US2199481068"/>
-        <filter val="US22160N1090"/>
-        <filter val="US22788C1053"/>
-        <filter val="US22822V1017"/>
-        <filter val="US23331A1097"/>
-        <filter val="US2333311072"/>
-        <filter val="US2358511028"/>
-        <filter val="US23804L1035"/>
-        <filter val="US2473617023"/>
-        <filter val="US25179M1036"/>
-        <filter val="US2521311074"/>
-        <filter val="US25278X1090"/>
-        <filter val="US2538681030"/>
-        <filter val="US2566771059"/>
-        <filter val="US2567461080"/>
-        <filter val="US25746U1097"/>
-        <filter val="US2605571031"/>
-        <filter val="US26142V1052"/>
-        <filter val="US26441C2044"/>
-        <filter val="US26614N1028"/>
-        <filter val="US2681501092"/>
-        <filter val="US26875P1012"/>
-        <filter val="US26884L1098"/>
-        <filter val="US2787681061"/>
-        <filter val="US28176E1082"/>
-        <filter val="US2910111044"/>
-        <filter val="US29362U1043"/>
-        <filter val="US29364G1031"/>
-        <filter val="US2944291051"/>
-        <filter val="US29444U7000"/>
-        <filter val="US29452E1010"/>
-        <filter val="US29472R1086"/>
-        <filter val="US29530P1021"/>
-        <filter val="US29670G1022"/>
-        <filter val="US30034W1062"/>
-        <filter val="US30040W1080"/>
-        <filter val="US30190A1043"/>
-        <filter val="US3021301094"/>
-        <filter val="US30231G1022"/>
-        <filter val="US3032501047"/>
-        <filter val="US31488V1070"/>
-        <filter val="US31620M1062"/>
-        <filter val="US31620R3030"/>
-        <filter val="US3167731005"/>
-        <filter val="US31946M1036"/>
-        <filter val="US3364331070"/>
-        <filter val="US3377381088"/>
-        <filter val="US3379321074"/>
-        <filter val="US34959J1088"/>
-        <filter val="US3635761097"/>
-        <filter val="US3666511072"/>
-        <filter val="US3695501086"/>
-        <filter val="US3703341046"/>
-        <filter val="US3724601055"/>
-        <filter val="US37940X1028"/>
-        <filter val="US3841091040"/>
-        <filter val="US4228061093"/>
-        <filter val="US4228062083"/>
-        <filter val="US4262811015"/>
-        <filter val="US4278661081"/>
-        <filter val="US4364401012"/>
-        <filter val="US4385161066"/>
-        <filter val="US4404521001"/>
-        <filter val="US4435106079"/>
-        <filter val="US4448591028"/>
-        <filter val="US4456581077"/>
-        <filter val="US4461501045"/>
-        <filter val="US4485791028"/>
-        <filter val="US45167R1041"/>
-        <filter val="US45168D1046"/>
-        <filter val="US45337C1027"/>
-        <filter val="US45687V1061"/>
-        <filter val="US4576693075"/>
-        <filter val="US45841N1072"/>
-        <filter val="US45866F1049"/>
-        <filter val="US4595061015"/>
-        <filter val="US4601461035"/>
-        <filter val="US46187W1071"/>
-        <filter val="US46222L1089"/>
-        <filter val="US46266C1053"/>
-        <filter val="US46284V1017"/>
-        <filter val="US46982L1089"/>
-        <filter val="US48251W1045"/>
-        <filter val="US49177J1025"/>
-        <filter val="US49271V1008"/>
-        <filter val="US4932671088"/>
-        <filter val="US49456B1017"/>
-        <filter val="US5007541064"/>
-        <filter val="US50212V1008"/>
-        <filter val="US5024311095"/>
-        <filter val="US5049221055"/>
-        <filter val="US5184391044"/>
-        <filter val="US5253271028"/>
-        <filter val="US5312297550"/>
-        <filter val="US5380341090"/>
-        <filter val="US5398301094"/>
-        <filter val="US5404241086"/>
-        <filter val="US55261F1049"/>
-        <filter val="US55354G1004"/>
-        <filter val="US56585A1025"/>
-        <filter val="US5705351048"/>
-        <filter val="US5717481023"/>
-        <filter val="US5732841060"/>
-        <filter val="US5738741041"/>
-        <filter val="US5797802064"/>
-        <filter val="US59156R1086"/>
-        <filter val="US5926881054"/>
-        <filter val="US5950171042"/>
-        <filter val="US59522J1034"/>
-        <filter val="US6092071058"/>
-        <filter val="US60937P1066"/>
-        <filter val="US62944T1051"/>
-        <filter val="US6311031081"/>
-        <filter val="US6323071042"/>
-        <filter val="US64125C1099"/>
-        <filter val="US65339F1012"/>
-        <filter val="US6541061031"/>
-        <filter val="US6556631025"/>
-        <filter val="US6558441084"/>
-        <filter val="US6668071029"/>
-        <filter val="US6703461052"/>
-        <filter val="US67059N1081"/>
-        <filter val="US6745991058"/>
-        <filter val="US6792951054"/>
-        <filter val="US6795801009"/>
-        <filter val="US6819191064"/>
-        <filter val="US6821891057"/>
-        <filter val="US69331C1080"/>
-        <filter val="US6934751057"/>
-        <filter val="US6935061076"/>
-        <filter val="US69351T1060"/>
-        <filter val="US69370C1009"/>
-        <filter val="US70432V1026"/>
-        <filter val="US7134481081"/>
-        <filter val="US7181721090"/>
-        <filter val="US7185461040"/>
-        <filter val="US74144T1088"/>
-        <filter val="US74251V1026"/>
-        <filter val="US7433151039"/>
-        <filter val="US74340W1036"/>
-        <filter val="US7443201022"/>
-        <filter val="US74624M1027"/>
-        <filter val="US74743L1008"/>
-        <filter val="US74762E1029"/>
-        <filter val="US75513E1010"/>
-        <filter val="US7561091049"/>
-        <filter val="US75734B1008"/>
-        <filter val="US75886F1075"/>
-        <filter val="US7710491033"/>
-        <filter val="US77311W1018"/>
-        <filter val="US7731211089"/>
-        <filter val="US7739031091"/>
-        <filter val="US7757111049"/>
-        <filter val="US7766961061"/>
-        <filter val="US78410G1040"/>
-        <filter val="US79589L1061"/>
-        <filter val="US81141R1005"/>
-        <filter val="US8168511090"/>
-        <filter val="US8326964058"/>
-        <filter val="US83304A1060"/>
-        <filter val="US8334451098"/>
-        <filter val="US83406F1021"/>
-        <filter val="US83444M1018"/>
-        <filter val="US8425871071"/>
-        <filter val="US8522341036"/>
-        <filter val="US8552441094"/>
-        <filter val="US8581191009"/>
-        <filter val="US8666741041"/>
-        <filter val="US86800U3023"/>
-        <filter val="US8716071076"/>
-        <filter val="US8740541094"/>
-        <filter val="US8760301072"/>
-        <filter val="US8793601050"/>
-        <filter val="US8807701029"/>
-        <filter val="US88160R1014"/>
-        <filter val="US8825081040"/>
-        <filter val="US88262P1021"/>
-        <filter val="US8832031012"/>
-        <filter val="US88339J1051"/>
-        <filter val="US8835561023"/>
-        <filter val="US8887871080"/>
-        <filter val="US8923561067"/>
-        <filter val="US8926721064"/>
-        <filter val="US8936411003"/>
-        <filter val="US89400J1079"/>
-        <filter val="US89417E1091"/>
-        <filter val="US8962391004"/>
-        <filter val="US89832Q1094"/>
-        <filter val="US9022521051"/>
-        <filter val="US9026531049"/>
-        <filter val="US9078181081"/>
-        <filter val="US9100471096"/>
-        <filter val="US92338C1036"/>
-        <filter val="US92532F1003"/>
-        <filter val="US92840M1027"/>
-        <filter val="US9291601097"/>
-        <filter val="US92939U1060"/>
-        <filter val="US94106L1098"/>
-        <filter val="US9418481035"/>
-        <filter val="US9621661043"/>
-        <filter val="US9694571004"/>
-        <filter val="US98138H1014"/>
-        <filter val="US98389B1008"/>
-        <filter val="US98419M1009"/>
-        <filter val="US9884981013"/>
-        <filter val="US98954M2008"/>
-        <filter val="US98956P1021"/>
-        <filter val="US98980G1022"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="3">
-      <filters>
-        <filter val="#N/A"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:D1634" xr:uid="{3DC52ED4-B602-4882-BC7B-91894D5F69EC}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>

--- a/CB-Achmea/2025/Uitsluitingen.xlsx
+++ b/CB-Achmea/2025/Uitsluitingen.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7c741cee80ec8cf3/Financieel/IndexFondsenOnderzoek/KeuzeWelkIndexFonds/OnderzoekPerFonds/CB-Achmea/2025/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="66" documentId="11_AD4D7A0C205A6B9A452FA8E75FDB70E25BDEDD8D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7AB794AB-ACB9-45B3-88E7-8CE0FE665958}"/>
+  <xr:revisionPtr revIDLastSave="67" documentId="11_AD4D7A0C205A6B9A452FA8E75FDB70E25BDEDD8D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7C940C5-19D7-4FED-932E-D07069F5493F}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
